--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121346709</v>
+        <v>121347308</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585866</v>
+        <v>585988</v>
       </c>
       <c r="R2" t="n">
-        <v>7084575</v>
+        <v>7084426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347495</v>
+        <v>121346096</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586092</v>
+        <v>585791</v>
       </c>
       <c r="R3" t="n">
-        <v>7084449</v>
+        <v>7084728</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347298</v>
+        <v>121346558</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,51 +929,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585969</v>
+        <v>585813</v>
       </c>
       <c r="R4" t="n">
-        <v>7084411</v>
+        <v>7084662</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346090</v>
+        <v>121346622</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585825</v>
+        <v>585815</v>
       </c>
       <c r="R5" t="n">
-        <v>7084709</v>
+        <v>7084624</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346522</v>
+        <v>121346543</v>
       </c>
       <c r="B6" t="n">
-        <v>57348</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,31 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585825</v>
+        <v>585822</v>
       </c>
       <c r="R6" t="n">
-        <v>7084654</v>
+        <v>7084651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,12 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346096</v>
+        <v>121346000</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,21 +1269,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1299,10 +1293,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585791</v>
+        <v>585818</v>
       </c>
       <c r="R7" t="n">
-        <v>7084728</v>
+        <v>7084786</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1338,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1371,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347539</v>
+        <v>121346576</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1411,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585948</v>
+        <v>585803</v>
       </c>
       <c r="R8" t="n">
-        <v>7084466</v>
+        <v>7084658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1446,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1456,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346558</v>
+        <v>121347511</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585813</v>
+        <v>586046</v>
       </c>
       <c r="R9" t="n">
-        <v>7084662</v>
+        <v>7084490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1558,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1595,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347731</v>
+        <v>121346034</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585899</v>
+        <v>585813</v>
       </c>
       <c r="R10" t="n">
-        <v>7084492</v>
+        <v>7084756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1670,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,22 +1694,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346000</v>
+        <v>121346437</v>
       </c>
       <c r="B11" t="n">
-        <v>57348</v>
+        <v>90715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1723,21 +1722,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1747,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585818</v>
+        <v>585813</v>
       </c>
       <c r="R11" t="n">
-        <v>7084786</v>
+        <v>7084694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1792,12 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1824,10 +1818,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347308</v>
+        <v>121347539</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,52 +1830,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585988</v>
+        <v>585948</v>
       </c>
       <c r="R12" t="n">
-        <v>7084426</v>
+        <v>7084466</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,22 +1918,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346543</v>
+        <v>121346709</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1962,42 +1942,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585822</v>
+        <v>585866</v>
       </c>
       <c r="R13" t="n">
-        <v>7084651</v>
+        <v>7084575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2029,7 +2005,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,7 +2015,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347019</v>
+        <v>121346090</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,42 +2054,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585857</v>
+        <v>585825</v>
       </c>
       <c r="R14" t="n">
-        <v>7084489</v>
+        <v>7084709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2117,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2127,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,22 +2142,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347424</v>
+        <v>121347517</v>
       </c>
       <c r="B15" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,39 +2170,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586076</v>
+        <v>585965</v>
       </c>
       <c r="R15" t="n">
-        <v>7084414</v>
+        <v>7084448</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2262,7 +2229,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2272,12 +2239,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2304,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347517</v>
+        <v>121347424</v>
       </c>
       <c r="B16" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,34 +2282,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585965</v>
+        <v>586076</v>
       </c>
       <c r="R16" t="n">
-        <v>7084448</v>
+        <v>7084414</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2346,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2356,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346594</v>
+        <v>121346703</v>
       </c>
       <c r="B17" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,7 +2423,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2460,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585801</v>
+        <v>585863</v>
       </c>
       <c r="R17" t="n">
-        <v>7084642</v>
+        <v>7084578</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2495,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2505,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,12 +2502,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2535,7 +2517,7 @@
         <v>121346810</v>
       </c>
       <c r="B18" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2644,10 +2626,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346435</v>
+        <v>121346522</v>
       </c>
       <c r="B19" t="n">
-        <v>78598</v>
+        <v>57351</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2660,34 +2642,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585819</v>
+        <v>585825</v>
       </c>
       <c r="R19" t="n">
-        <v>7084684</v>
+        <v>7084654</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2719,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2729,7 +2716,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2756,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347511</v>
+        <v>121347495</v>
       </c>
       <c r="B20" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2796,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586046</v>
+        <v>586092</v>
       </c>
       <c r="R20" t="n">
-        <v>7084490</v>
+        <v>7084449</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2831,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2841,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2868,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347155</v>
+        <v>121347298</v>
       </c>
       <c r="B21" t="n">
-        <v>98071</v>
+        <v>57504</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2880,55 +2872,55 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585879</v>
+        <v>585969</v>
       </c>
       <c r="R21" t="n">
-        <v>7084451</v>
+        <v>7084411</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2957,7 +2949,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2967,7 +2959,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,10 +2986,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347537</v>
+        <v>121347327</v>
       </c>
       <c r="B22" t="n">
-        <v>57364</v>
+        <v>78601</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3010,39 +3002,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585943</v>
+        <v>586037</v>
       </c>
       <c r="R22" t="n">
-        <v>7084462</v>
+        <v>7084389</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,22 +3086,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346703</v>
+        <v>121347155</v>
       </c>
       <c r="B23" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3146,7 +3133,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3165,10 +3152,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585863</v>
+        <v>585879</v>
       </c>
       <c r="R23" t="n">
-        <v>7084578</v>
+        <v>7084451</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3200,7 +3187,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3210,7 +3197,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3237,10 +3224,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346034</v>
+        <v>121347537</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>57367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3253,34 +3240,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585813</v>
+        <v>585943</v>
       </c>
       <c r="R24" t="n">
-        <v>7084756</v>
+        <v>7084462</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3312,7 +3304,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3322,7 +3314,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3349,10 +3341,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347327</v>
+        <v>121347731</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3389,10 +3381,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586037</v>
+        <v>585899</v>
       </c>
       <c r="R25" t="n">
-        <v>7084389</v>
+        <v>7084492</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,7 +3416,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3434,7 +3426,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,10 +3453,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346622</v>
+        <v>121347310</v>
       </c>
       <c r="B26" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3501,10 +3493,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585815</v>
+        <v>585983</v>
       </c>
       <c r="R26" t="n">
-        <v>7084624</v>
+        <v>7084425</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3536,7 +3528,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3546,7 +3538,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3573,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346437</v>
+        <v>121346435</v>
       </c>
       <c r="B27" t="n">
-        <v>90705</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3589,21 +3581,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3613,10 +3605,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585813</v>
+        <v>585819</v>
       </c>
       <c r="R27" t="n">
-        <v>7084694</v>
+        <v>7084684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,22 +3665,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346576</v>
+        <v>121346594</v>
       </c>
       <c r="B28" t="n">
-        <v>90687</v>
+        <v>98081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,38 +3689,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585803</v>
+        <v>585801</v>
       </c>
       <c r="R28" t="n">
-        <v>7084658</v>
+        <v>7084642</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3756,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3766,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,10 +3793,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347310</v>
+        <v>121347019</v>
       </c>
       <c r="B29" t="n">
-        <v>78598</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,38 +3805,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585983</v>
+        <v>585857</v>
       </c>
       <c r="R29" t="n">
-        <v>7084425</v>
+        <v>7084489</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346576</v>
+        <v>121347511</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585803</v>
+        <v>586046</v>
       </c>
       <c r="R8" t="n">
-        <v>7084658</v>
+        <v>7084490</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347511</v>
+        <v>121346576</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586046</v>
+        <v>585803</v>
       </c>
       <c r="R9" t="n">
-        <v>7084490</v>
+        <v>7084658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -3565,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346435</v>
+        <v>121346594</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3577,38 +3577,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585819</v>
+        <v>585801</v>
       </c>
       <c r="R27" t="n">
-        <v>7084684</v>
+        <v>7084642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3644,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3654,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,19 +3669,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346594</v>
+        <v>121347019</v>
       </c>
       <c r="B28" t="n">
         <v>98081</v>
@@ -3712,7 +3716,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3721,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585801</v>
+        <v>585857</v>
       </c>
       <c r="R28" t="n">
-        <v>7084642</v>
+        <v>7084489</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3756,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3766,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3793,10 +3797,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347019</v>
+        <v>121346435</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,42 +3809,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585857</v>
+        <v>585819</v>
       </c>
       <c r="R29" t="n">
-        <v>7084489</v>
+        <v>7084684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -913,7 +913,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346558</v>
+        <v>121346622</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585813</v>
+        <v>585815</v>
       </c>
       <c r="R4" t="n">
-        <v>7084662</v>
+        <v>7084624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1025,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346622</v>
+        <v>121346558</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585815</v>
+        <v>585813</v>
       </c>
       <c r="R5" t="n">
-        <v>7084624</v>
+        <v>7084662</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1370,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347511</v>
+        <v>121346576</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1386,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,10 +1410,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586046</v>
+        <v>585803</v>
       </c>
       <c r="R8" t="n">
-        <v>7084490</v>
+        <v>7084658</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,10 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346576</v>
+        <v>121347511</v>
       </c>
       <c r="B9" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,21 +1498,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585803</v>
+        <v>586046</v>
       </c>
       <c r="R9" t="n">
-        <v>7084658</v>
+        <v>7084490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346034</v>
+        <v>121346437</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1610,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1637,7 +1637,7 @@
         <v>585813</v>
       </c>
       <c r="R10" t="n">
-        <v>7084756</v>
+        <v>7084694</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,22 +1694,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346437</v>
+        <v>121347539</v>
       </c>
       <c r="B11" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,21 +1722,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585813</v>
+        <v>585948</v>
       </c>
       <c r="R11" t="n">
-        <v>7084694</v>
+        <v>7084466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1781,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347539</v>
+        <v>121346034</v>
       </c>
       <c r="B12" t="n">
         <v>78601</v>
@@ -1858,10 +1858,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585948</v>
+        <v>585813</v>
       </c>
       <c r="R12" t="n">
-        <v>7084466</v>
+        <v>7084756</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,12 +1918,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347424</v>
+        <v>121346810</v>
       </c>
       <c r="B16" t="n">
-        <v>57351</v>
+        <v>97035</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,43 +2278,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586076</v>
+        <v>585874</v>
       </c>
       <c r="R16" t="n">
-        <v>7084414</v>
+        <v>7084559</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2346,7 +2341,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2356,12 +2351,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2514,10 +2504,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346810</v>
+        <v>121347424</v>
       </c>
       <c r="B18" t="n">
-        <v>97035</v>
+        <v>57351</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,38 +2516,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585874</v>
+        <v>586076</v>
       </c>
       <c r="R18" t="n">
-        <v>7084559</v>
+        <v>7084414</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2594,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3565,10 +3565,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346594</v>
+        <v>121346435</v>
       </c>
       <c r="B27" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3577,42 +3577,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585801</v>
+        <v>585819</v>
       </c>
       <c r="R27" t="n">
-        <v>7084642</v>
+        <v>7084684</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3644,7 +3640,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3654,7 +3650,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,19 +3665,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347019</v>
+        <v>121346594</v>
       </c>
       <c r="B28" t="n">
         <v>98081</v>
@@ -3716,7 +3712,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3725,10 +3721,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585857</v>
+        <v>585801</v>
       </c>
       <c r="R28" t="n">
-        <v>7084489</v>
+        <v>7084642</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3756,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3766,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,10 +3793,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346435</v>
+        <v>121347019</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,38 +3805,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585819</v>
+        <v>585857</v>
       </c>
       <c r="R29" t="n">
-        <v>7084684</v>
+        <v>7084489</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121347308</v>
+        <v>121346000</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585988</v>
+        <v>585818</v>
       </c>
       <c r="R2" t="n">
-        <v>7084426</v>
+        <v>7084786</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346096</v>
+        <v>121347537</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +808,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585791</v>
+        <v>585943</v>
       </c>
       <c r="R3" t="n">
-        <v>7084728</v>
+        <v>7084462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,19 +897,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346622</v>
+        <v>121346709</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -953,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585815</v>
+        <v>585866</v>
       </c>
       <c r="R4" t="n">
-        <v>7084624</v>
+        <v>7084575</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346558</v>
+        <v>121346522</v>
       </c>
       <c r="B5" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585813</v>
+        <v>585825</v>
       </c>
       <c r="R5" t="n">
-        <v>7084662</v>
+        <v>7084654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1131,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346543</v>
+        <v>121346558</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,42 +1155,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585822</v>
+        <v>585813</v>
       </c>
       <c r="R6" t="n">
-        <v>7084651</v>
+        <v>7084662</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346000</v>
+        <v>121346810</v>
       </c>
       <c r="B7" t="n">
-        <v>57351</v>
+        <v>97035</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585818</v>
+        <v>585874</v>
       </c>
       <c r="R7" t="n">
-        <v>7084786</v>
+        <v>7084559</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,22 +1355,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346576</v>
+        <v>121346435</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1410,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585803</v>
+        <v>585819</v>
       </c>
       <c r="R8" t="n">
-        <v>7084658</v>
+        <v>7084684</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,22 +1467,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347511</v>
+        <v>121347298</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,37 +1495,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586046</v>
+        <v>585969</v>
       </c>
       <c r="R9" t="n">
-        <v>7084490</v>
+        <v>7084411</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1557,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1593,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346437</v>
+        <v>121347495</v>
       </c>
       <c r="B10" t="n">
-        <v>90715</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,21 +1621,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1634,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585813</v>
+        <v>586092</v>
       </c>
       <c r="R10" t="n">
-        <v>7084694</v>
+        <v>7084449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1717,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347539</v>
+        <v>121346437</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>90715</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,21 +1733,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1746,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585948</v>
+        <v>585813</v>
       </c>
       <c r="R11" t="n">
-        <v>7084466</v>
+        <v>7084694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1781,7 +1792,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1791,7 +1802,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346034</v>
+        <v>121346576</v>
       </c>
       <c r="B12" t="n">
-        <v>78601</v>
+        <v>90697</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1834,21 +1845,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,10 +1869,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585813</v>
+        <v>585803</v>
       </c>
       <c r="R12" t="n">
-        <v>7084756</v>
+        <v>7084658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1893,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1903,7 +1914,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,19 +1929,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346709</v>
+        <v>121347539</v>
       </c>
       <c r="B13" t="n">
         <v>78601</v>
@@ -1970,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585866</v>
+        <v>585948</v>
       </c>
       <c r="R13" t="n">
-        <v>7084575</v>
+        <v>7084466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2005,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2015,7 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346090</v>
+        <v>121347155</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,38 +2065,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585825</v>
+        <v>585879</v>
       </c>
       <c r="R14" t="n">
-        <v>7084709</v>
+        <v>7084451</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2117,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2127,7 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2154,7 +2179,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347517</v>
+        <v>121346090</v>
       </c>
       <c r="B15" t="n">
         <v>78601</v>
@@ -2194,10 +2219,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585965</v>
+        <v>585825</v>
       </c>
       <c r="R15" t="n">
-        <v>7084448</v>
+        <v>7084709</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2229,7 +2254,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2239,7 +2264,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346810</v>
+        <v>121347731</v>
       </c>
       <c r="B16" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2278,25 +2303,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2306,10 +2331,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585874</v>
+        <v>585899</v>
       </c>
       <c r="R16" t="n">
-        <v>7084559</v>
+        <v>7084492</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2341,7 +2366,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2351,7 +2376,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2366,19 +2391,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346703</v>
+        <v>121347308</v>
       </c>
       <c r="B17" t="n">
         <v>98081</v>
@@ -2413,7 +2438,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2432,10 +2457,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585863</v>
+        <v>585988</v>
       </c>
       <c r="R17" t="n">
-        <v>7084578</v>
+        <v>7084426</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,7 +2492,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2502,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,10 +2651,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346522</v>
+        <v>121346034</v>
       </c>
       <c r="B19" t="n">
-        <v>57351</v>
+        <v>78601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2642,39 +2667,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585825</v>
+        <v>585813</v>
       </c>
       <c r="R19" t="n">
-        <v>7084654</v>
+        <v>7084756</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,12 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347495</v>
+        <v>121346543</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2760,38 +2775,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586092</v>
+        <v>585822</v>
       </c>
       <c r="R20" t="n">
-        <v>7084449</v>
+        <v>7084651</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2852,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347298</v>
+        <v>121346096</v>
       </c>
       <c r="B21" t="n">
-        <v>57504</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,51 +2895,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585969</v>
+        <v>585791</v>
       </c>
       <c r="R21" t="n">
-        <v>7084411</v>
+        <v>7084728</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2949,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2974,22 +2979,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347327</v>
+        <v>121347019</v>
       </c>
       <c r="B22" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2998,38 +3003,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586037</v>
+        <v>585857</v>
       </c>
       <c r="R22" t="n">
-        <v>7084389</v>
+        <v>7084489</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3080,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,7 +3107,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347155</v>
+        <v>121346703</v>
       </c>
       <c r="B23" t="n">
         <v>98081</v>
@@ -3133,7 +3142,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3152,10 +3161,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585879</v>
+        <v>585863</v>
       </c>
       <c r="R23" t="n">
-        <v>7084451</v>
+        <v>7084578</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3187,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3197,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3224,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347537</v>
+        <v>121347511</v>
       </c>
       <c r="B24" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3240,39 +3249,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585943</v>
+        <v>586046</v>
       </c>
       <c r="R24" t="n">
-        <v>7084462</v>
+        <v>7084490</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3304,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3314,7 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3329,22 +3333,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347731</v>
+        <v>121346594</v>
       </c>
       <c r="B25" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3353,38 +3357,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585899</v>
+        <v>585801</v>
       </c>
       <c r="R25" t="n">
-        <v>7084492</v>
+        <v>7084642</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3416,7 +3424,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3426,7 +3434,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3565,7 +3573,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346435</v>
+        <v>121347517</v>
       </c>
       <c r="B27" t="n">
         <v>78601</v>
@@ -3605,10 +3613,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585819</v>
+        <v>585965</v>
       </c>
       <c r="R27" t="n">
-        <v>7084684</v>
+        <v>7084448</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3650,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3677,10 +3685,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346594</v>
+        <v>121347327</v>
       </c>
       <c r="B28" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3689,42 +3697,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585801</v>
+        <v>586037</v>
       </c>
       <c r="R28" t="n">
-        <v>7084642</v>
+        <v>7084389</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3756,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3766,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3793,10 +3797,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347019</v>
+        <v>121346622</v>
       </c>
       <c r="B29" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3805,42 +3809,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585857</v>
+        <v>585815</v>
       </c>
       <c r="R29" t="n">
-        <v>7084489</v>
+        <v>7084624</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346558</v>
+        <v>121346810</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>97035</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585813</v>
+        <v>585874</v>
       </c>
       <c r="R6" t="n">
-        <v>7084662</v>
+        <v>7084559</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,22 +1243,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346810</v>
+        <v>121346558</v>
       </c>
       <c r="B7" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,25 +1267,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585874</v>
+        <v>585813</v>
       </c>
       <c r="R7" t="n">
-        <v>7084559</v>
+        <v>7084662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,12 +1355,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346543</v>
+        <v>121346096</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2775,42 +2775,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585822</v>
+        <v>585791</v>
       </c>
       <c r="R20" t="n">
-        <v>7084651</v>
+        <v>7084728</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2842,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2852,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2879,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346096</v>
+        <v>121346543</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2891,38 +2887,42 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585791</v>
+        <v>585822</v>
       </c>
       <c r="R21" t="n">
-        <v>7084728</v>
+        <v>7084651</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121346000</v>
+        <v>121347298</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>57504</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,51 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585818</v>
+        <v>585969</v>
       </c>
       <c r="R2" t="n">
-        <v>7084786</v>
+        <v>7084411</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347537</v>
+        <v>121347308</v>
       </c>
       <c r="B3" t="n">
-        <v>57367</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,43 +813,52 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585943</v>
+        <v>585988</v>
       </c>
       <c r="R3" t="n">
-        <v>7084462</v>
+        <v>7084426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346709</v>
+        <v>121346703</v>
       </c>
       <c r="B4" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,38 +939,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585866</v>
+        <v>585863</v>
       </c>
       <c r="R4" t="n">
-        <v>7084575</v>
+        <v>7084578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +1016,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +1026,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1041,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346522</v>
+        <v>121346437</v>
       </c>
       <c r="B5" t="n">
-        <v>57351</v>
+        <v>90727</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1069,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585825</v>
+        <v>585813</v>
       </c>
       <c r="R5" t="n">
-        <v>7084654</v>
+        <v>7084694</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,22 +1153,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346810</v>
+        <v>121346034</v>
       </c>
       <c r="B6" t="n">
-        <v>97035</v>
+        <v>78604</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,25 +1177,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585874</v>
+        <v>585813</v>
       </c>
       <c r="R6" t="n">
-        <v>7084559</v>
+        <v>7084756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346558</v>
+        <v>121346090</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1295,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585813</v>
+        <v>585825</v>
       </c>
       <c r="R7" t="n">
-        <v>7084662</v>
+        <v>7084709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,22 +1377,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346435</v>
+        <v>121347424</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,34 +1405,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585819</v>
+        <v>586076</v>
       </c>
       <c r="R8" t="n">
-        <v>7084684</v>
+        <v>7084414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1479,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347298</v>
+        <v>121347731</v>
       </c>
       <c r="B9" t="n">
-        <v>57504</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,51 +1527,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585969</v>
+        <v>585899</v>
       </c>
       <c r="R9" t="n">
-        <v>7084411</v>
+        <v>7084492</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1568,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,22 +1611,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347495</v>
+        <v>121347511</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586092</v>
+        <v>586046</v>
       </c>
       <c r="R10" t="n">
-        <v>7084449</v>
+        <v>7084490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1708,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346437</v>
+        <v>121347155</v>
       </c>
       <c r="B11" t="n">
-        <v>90715</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1729,38 +1747,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585813</v>
+        <v>585879</v>
       </c>
       <c r="R11" t="n">
-        <v>7084694</v>
+        <v>7084451</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1792,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,22 +1849,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346576</v>
+        <v>121347495</v>
       </c>
       <c r="B12" t="n">
-        <v>90697</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,21 +1877,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1869,10 +1901,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585803</v>
+        <v>586092</v>
       </c>
       <c r="R12" t="n">
-        <v>7084658</v>
+        <v>7084449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1941,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347539</v>
+        <v>121346522</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1957,34 +1989,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585948</v>
+        <v>585825</v>
       </c>
       <c r="R13" t="n">
-        <v>7084466</v>
+        <v>7084654</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2053,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2063,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,22 +2083,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347155</v>
+        <v>121346594</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,17 +2130,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2107,10 +2139,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585879</v>
+        <v>585801</v>
       </c>
       <c r="R14" t="n">
-        <v>7084451</v>
+        <v>7084642</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,7 +2174,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2184,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,22 +2199,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346090</v>
+        <v>121346810</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>97048</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,25 +2223,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2219,10 +2251,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585825</v>
+        <v>585874</v>
       </c>
       <c r="R15" t="n">
-        <v>7084709</v>
+        <v>7084559</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2254,7 +2286,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2296,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2323,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347731</v>
+        <v>121347310</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2331,10 +2363,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585899</v>
+        <v>585983</v>
       </c>
       <c r="R16" t="n">
-        <v>7084492</v>
+        <v>7084425</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2366,7 +2398,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2376,7 +2408,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,10 +2435,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347308</v>
+        <v>121346435</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2415,52 +2447,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585988</v>
+        <v>585819</v>
       </c>
       <c r="R17" t="n">
-        <v>7084426</v>
+        <v>7084684</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2492,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2502,7 +2520,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347424</v>
+        <v>121347327</v>
       </c>
       <c r="B18" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2545,39 +2563,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586076</v>
+        <v>586037</v>
       </c>
       <c r="R18" t="n">
-        <v>7084414</v>
+        <v>7084389</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2609,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2619,12 +2632,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2639,22 +2647,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346034</v>
+        <v>121346096</v>
       </c>
       <c r="B19" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2691,10 +2699,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585813</v>
+        <v>585791</v>
       </c>
       <c r="R19" t="n">
-        <v>7084756</v>
+        <v>7084728</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2726,7 +2734,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,7 +2744,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2751,22 +2759,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346096</v>
+        <v>121347539</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,10 +2811,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585791</v>
+        <v>585948</v>
       </c>
       <c r="R20" t="n">
-        <v>7084728</v>
+        <v>7084466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2838,7 +2846,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2848,7 +2856,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2875,10 +2883,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346543</v>
+        <v>121347517</v>
       </c>
       <c r="B21" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2887,42 +2895,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585822</v>
+        <v>585965</v>
       </c>
       <c r="R21" t="n">
-        <v>7084651</v>
+        <v>7084448</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,7 +2958,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2968,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,22 +2983,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347019</v>
+        <v>121346622</v>
       </c>
       <c r="B22" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,42 +3007,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585857</v>
+        <v>585815</v>
       </c>
       <c r="R22" t="n">
-        <v>7084489</v>
+        <v>7084624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3080,7 +3080,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3107,10 +3107,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346703</v>
+        <v>121346709</v>
       </c>
       <c r="B23" t="n">
-        <v>98081</v>
+        <v>78604</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,52 +3119,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585863</v>
+        <v>585866</v>
       </c>
       <c r="R23" t="n">
-        <v>7084578</v>
+        <v>7084575</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,7 +3182,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3192,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,22 +3207,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347511</v>
+        <v>121346000</v>
       </c>
       <c r="B24" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3249,21 +3235,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3273,10 +3259,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586046</v>
+        <v>585818</v>
       </c>
       <c r="R24" t="n">
-        <v>7084490</v>
+        <v>7084786</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,7 +3294,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3304,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,10 +3336,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346594</v>
+        <v>121346543</v>
       </c>
       <c r="B25" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,7 +3371,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3389,10 +3380,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585801</v>
+        <v>585822</v>
       </c>
       <c r="R25" t="n">
-        <v>7084642</v>
+        <v>7084651</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,7 +3415,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3434,7 +3425,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,10 +3452,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347310</v>
+        <v>121346576</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>90709</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3477,21 +3468,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3501,10 +3492,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585983</v>
+        <v>585803</v>
       </c>
       <c r="R26" t="n">
-        <v>7084425</v>
+        <v>7084658</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3536,7 +3527,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3546,7 +3537,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3573,10 +3564,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347517</v>
+        <v>121346558</v>
       </c>
       <c r="B27" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3613,10 +3604,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585965</v>
+        <v>585813</v>
       </c>
       <c r="R27" t="n">
-        <v>7084448</v>
+        <v>7084662</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,7 +3639,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3649,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,22 +3664,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347327</v>
+        <v>121347019</v>
       </c>
       <c r="B28" t="n">
-        <v>78601</v>
+        <v>98094</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,38 +3688,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586037</v>
+        <v>585857</v>
       </c>
       <c r="R28" t="n">
-        <v>7084389</v>
+        <v>7084489</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3755,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3765,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,10 +3792,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346622</v>
+        <v>121347537</v>
       </c>
       <c r="B29" t="n">
-        <v>78601</v>
+        <v>57367</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3813,34 +3808,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585815</v>
+        <v>585943</v>
       </c>
       <c r="R29" t="n">
-        <v>7084624</v>
+        <v>7084462</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121347298</v>
+        <v>121347308</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,29 +713,29 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585969</v>
+        <v>585988</v>
       </c>
       <c r="R2" t="n">
-        <v>7084411</v>
+        <v>7084426</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347308</v>
+        <v>121347539</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,52 +813,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585988</v>
+        <v>585948</v>
       </c>
       <c r="R3" t="n">
-        <v>7084426</v>
+        <v>7084466</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346703</v>
+        <v>121347155</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,7 +948,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -981,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585863</v>
+        <v>585879</v>
       </c>
       <c r="R4" t="n">
-        <v>7084578</v>
+        <v>7084451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1016,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1026,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346437</v>
+        <v>121346703</v>
       </c>
       <c r="B5" t="n">
-        <v>90727</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,38 +1051,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585813</v>
+        <v>585863</v>
       </c>
       <c r="R5" t="n">
-        <v>7084694</v>
+        <v>7084578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,22 +1153,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346034</v>
+        <v>121347019</v>
       </c>
       <c r="B6" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,38 +1177,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585813</v>
+        <v>585857</v>
       </c>
       <c r="R6" t="n">
-        <v>7084756</v>
+        <v>7084489</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1244,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,19 +1269,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346090</v>
+        <v>121347310</v>
       </c>
       <c r="B7" t="n">
         <v>78604</v>
@@ -1317,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585825</v>
+        <v>585983</v>
       </c>
       <c r="R7" t="n">
-        <v>7084709</v>
+        <v>7084425</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1366,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,22 +1381,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347424</v>
+        <v>121347731</v>
       </c>
       <c r="B8" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,39 +1409,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586076</v>
+        <v>585899</v>
       </c>
       <c r="R8" t="n">
-        <v>7084414</v>
+        <v>7084492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,12 +1478,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,22 +1493,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347731</v>
+        <v>121346522</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,34 +1521,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585899</v>
+        <v>585825</v>
       </c>
       <c r="R9" t="n">
-        <v>7084492</v>
+        <v>7084654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,7 +1585,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1595,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,19 +1615,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347511</v>
+        <v>121347495</v>
       </c>
       <c r="B10" t="n">
         <v>78604</v>
@@ -1663,10 +1667,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586046</v>
+        <v>586092</v>
       </c>
       <c r="R10" t="n">
-        <v>7084490</v>
+        <v>7084449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,7 +1702,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,7 +1712,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,10 +1739,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347155</v>
+        <v>121347424</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>57351</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,52 +1751,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585879</v>
+        <v>586076</v>
       </c>
       <c r="R11" t="n">
-        <v>7084451</v>
+        <v>7084414</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1829,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347495</v>
+        <v>121346543</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,38 +1873,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586092</v>
+        <v>585822</v>
       </c>
       <c r="R12" t="n">
-        <v>7084449</v>
+        <v>7084651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1950,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346522</v>
+        <v>121347517</v>
       </c>
       <c r="B13" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,39 +1993,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585825</v>
+        <v>585965</v>
       </c>
       <c r="R13" t="n">
-        <v>7084654</v>
+        <v>7084448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2053,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2063,12 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2089,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346594</v>
+        <v>121347537</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>57367</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2107,42 +2101,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585801</v>
+        <v>585943</v>
       </c>
       <c r="R14" t="n">
-        <v>7084642</v>
+        <v>7084462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2174,7 +2169,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2184,7 +2179,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2199,22 +2194,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346810</v>
+        <v>121347298</v>
       </c>
       <c r="B15" t="n">
-        <v>97048</v>
+        <v>57504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2223,41 +2218,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585874</v>
+        <v>585969</v>
       </c>
       <c r="R15" t="n">
-        <v>7084559</v>
+        <v>7084411</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2286,7 +2295,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2296,7 +2305,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2323,7 +2332,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347310</v>
+        <v>121346709</v>
       </c>
       <c r="B16" t="n">
         <v>78604</v>
@@ -2363,10 +2372,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585983</v>
+        <v>585866</v>
       </c>
       <c r="R16" t="n">
-        <v>7084425</v>
+        <v>7084575</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2398,7 +2407,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2408,7 +2417,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,10 +2444,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346435</v>
+        <v>121346576</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>90710</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2451,21 +2460,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2475,10 +2484,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585819</v>
+        <v>585803</v>
       </c>
       <c r="R17" t="n">
-        <v>7084684</v>
+        <v>7084658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2519,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,7 +2529,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2535,19 +2544,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347327</v>
+        <v>121346435</v>
       </c>
       <c r="B18" t="n">
         <v>78604</v>
@@ -2587,10 +2596,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586037</v>
+        <v>585819</v>
       </c>
       <c r="R18" t="n">
-        <v>7084389</v>
+        <v>7084684</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2631,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,7 +2641,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,19 +2656,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346096</v>
+        <v>121346558</v>
       </c>
       <c r="B19" t="n">
         <v>78604</v>
@@ -2699,10 +2708,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585791</v>
+        <v>585813</v>
       </c>
       <c r="R19" t="n">
-        <v>7084728</v>
+        <v>7084662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2734,7 +2743,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2744,7 +2753,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2771,7 +2780,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347539</v>
+        <v>121347511</v>
       </c>
       <c r="B20" t="n">
         <v>78604</v>
@@ -2811,10 +2820,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585948</v>
+        <v>586046</v>
       </c>
       <c r="R20" t="n">
-        <v>7084466</v>
+        <v>7084490</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2846,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2856,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2883,10 +2892,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347517</v>
+        <v>121346000</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>57351</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2899,21 +2908,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2923,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585965</v>
+        <v>585818</v>
       </c>
       <c r="R21" t="n">
-        <v>7084448</v>
+        <v>7084786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2958,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2968,7 +2977,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2983,12 +2997,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3107,10 +3121,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346709</v>
+        <v>121346437</v>
       </c>
       <c r="B23" t="n">
-        <v>78604</v>
+        <v>90728</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3123,21 +3137,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3147,10 +3161,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585866</v>
+        <v>585813</v>
       </c>
       <c r="R23" t="n">
-        <v>7084575</v>
+        <v>7084694</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3182,7 +3196,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3192,7 +3206,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3219,10 +3233,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346000</v>
+        <v>121347327</v>
       </c>
       <c r="B24" t="n">
-        <v>57351</v>
+        <v>78604</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3235,21 +3249,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3259,10 +3273,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585818</v>
+        <v>586037</v>
       </c>
       <c r="R24" t="n">
-        <v>7084786</v>
+        <v>7084389</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3294,7 +3308,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3304,12 +3318,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3336,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346543</v>
+        <v>121346096</v>
       </c>
       <c r="B25" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3348,42 +3357,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585822</v>
+        <v>585791</v>
       </c>
       <c r="R25" t="n">
-        <v>7084651</v>
+        <v>7084728</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3415,7 +3420,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3425,7 +3430,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3452,10 +3457,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346576</v>
+        <v>121346594</v>
       </c>
       <c r="B26" t="n">
-        <v>90709</v>
+        <v>98095</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,38 +3469,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585803</v>
+        <v>585801</v>
       </c>
       <c r="R26" t="n">
-        <v>7084658</v>
+        <v>7084642</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3527,7 +3536,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3537,7 +3546,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3564,7 +3573,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346558</v>
+        <v>121346090</v>
       </c>
       <c r="B27" t="n">
         <v>78604</v>
@@ -3604,10 +3613,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585813</v>
+        <v>585825</v>
       </c>
       <c r="R27" t="n">
-        <v>7084662</v>
+        <v>7084709</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3639,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3664,22 +3673,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347019</v>
+        <v>121346034</v>
       </c>
       <c r="B28" t="n">
-        <v>98094</v>
+        <v>78604</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3688,42 +3697,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585857</v>
+        <v>585813</v>
       </c>
       <c r="R28" t="n">
-        <v>7084489</v>
+        <v>7084756</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3755,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3765,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3780,22 +3785,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347537</v>
+        <v>121346810</v>
       </c>
       <c r="B29" t="n">
-        <v>57367</v>
+        <v>97049</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3804,43 +3809,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585943</v>
+        <v>585874</v>
       </c>
       <c r="R29" t="n">
-        <v>7084462</v>
+        <v>7084559</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121347308</v>
+        <v>121346543</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,17 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585988</v>
+        <v>585822</v>
       </c>
       <c r="R2" t="n">
-        <v>7084426</v>
+        <v>7084651</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347539</v>
+        <v>121347537</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>57370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,34 +807,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585948</v>
+        <v>585943</v>
       </c>
       <c r="R3" t="n">
-        <v>7084466</v>
+        <v>7084462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +896,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347155</v>
+        <v>121346096</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,52 +920,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585879</v>
+        <v>585791</v>
       </c>
       <c r="R4" t="n">
-        <v>7084451</v>
+        <v>7084728</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,22 +1008,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346703</v>
+        <v>121346435</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,52 +1032,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585863</v>
+        <v>585819</v>
       </c>
       <c r="R5" t="n">
-        <v>7084578</v>
+        <v>7084684</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1165,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121347019</v>
+        <v>121346810</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>97052</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,42 +1144,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585857</v>
+        <v>585874</v>
       </c>
       <c r="R6" t="n">
-        <v>7084489</v>
+        <v>7084559</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1244,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1254,7 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1269,22 +1232,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347310</v>
+        <v>121347495</v>
       </c>
       <c r="B7" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585983</v>
+        <v>586092</v>
       </c>
       <c r="R7" t="n">
-        <v>7084425</v>
+        <v>7084449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,7 +1329,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,10 +1356,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347731</v>
+        <v>121346622</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1433,10 +1396,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585899</v>
+        <v>585815</v>
       </c>
       <c r="R8" t="n">
-        <v>7084492</v>
+        <v>7084624</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1431,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1441,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,10 +1468,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346522</v>
+        <v>121347155</v>
       </c>
       <c r="B9" t="n">
-        <v>57351</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,31 +1480,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1550,10 +1522,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585825</v>
+        <v>585879</v>
       </c>
       <c r="R9" t="n">
-        <v>7084654</v>
+        <v>7084451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,7 +1557,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,12 +1567,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,10 +1594,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347495</v>
+        <v>121346000</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,21 +1610,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>586092</v>
+        <v>585818</v>
       </c>
       <c r="R10" t="n">
-        <v>7084449</v>
+        <v>7084786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1702,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1679,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1739,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347424</v>
+        <v>121347298</v>
       </c>
       <c r="B11" t="n">
-        <v>57351</v>
+        <v>57507</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1755,27 +1727,36 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1784,13 +1765,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586076</v>
+        <v>585969</v>
       </c>
       <c r="R11" t="n">
-        <v>7084414</v>
+        <v>7084411</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1819,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,12 +1810,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1837,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346543</v>
+        <v>121346576</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>90713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1873,42 +1849,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585822</v>
+        <v>585803</v>
       </c>
       <c r="R12" t="n">
-        <v>7084651</v>
+        <v>7084658</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347517</v>
+        <v>121346034</v>
       </c>
       <c r="B13" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2017,10 +1989,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585965</v>
+        <v>585813</v>
       </c>
       <c r="R13" t="n">
-        <v>7084448</v>
+        <v>7084756</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2089,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347537</v>
+        <v>121346090</v>
       </c>
       <c r="B14" t="n">
-        <v>57367</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2105,39 +2077,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585943</v>
+        <v>585825</v>
       </c>
       <c r="R14" t="n">
-        <v>7084462</v>
+        <v>7084709</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,7 +2136,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2179,7 +2146,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2206,10 +2173,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347298</v>
+        <v>121347019</v>
       </c>
       <c r="B15" t="n">
-        <v>57504</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2218,55 +2185,45 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585969</v>
+        <v>585857</v>
       </c>
       <c r="R15" t="n">
-        <v>7084411</v>
+        <v>7084489</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2295,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2320,22 +2277,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346709</v>
+        <v>121346522</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2348,34 +2305,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585866</v>
+        <v>585825</v>
       </c>
       <c r="R16" t="n">
-        <v>7084575</v>
+        <v>7084654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2407,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2417,7 +2379,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2432,22 +2399,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346576</v>
+        <v>121346594</v>
       </c>
       <c r="B17" t="n">
-        <v>90710</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2456,38 +2423,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585803</v>
+        <v>585801</v>
       </c>
       <c r="R17" t="n">
-        <v>7084658</v>
+        <v>7084642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2519,7 +2490,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2529,7 +2500,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2556,10 +2527,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346435</v>
+        <v>121347424</v>
       </c>
       <c r="B18" t="n">
-        <v>78604</v>
+        <v>57354</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,34 +2543,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585819</v>
+        <v>586076</v>
       </c>
       <c r="R18" t="n">
-        <v>7084684</v>
+        <v>7084414</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2631,7 +2607,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2641,7 +2617,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2668,10 +2649,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346558</v>
+        <v>121347511</v>
       </c>
       <c r="B19" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2708,10 +2689,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585813</v>
+        <v>586046</v>
       </c>
       <c r="R19" t="n">
-        <v>7084662</v>
+        <v>7084490</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2743,7 +2724,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2753,7 +2734,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2780,10 +2761,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347511</v>
+        <v>121347539</v>
       </c>
       <c r="B20" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2820,10 +2801,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586046</v>
+        <v>585948</v>
       </c>
       <c r="R20" t="n">
-        <v>7084490</v>
+        <v>7084466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2855,7 +2836,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2846,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,10 +2873,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346000</v>
+        <v>121346709</v>
       </c>
       <c r="B21" t="n">
-        <v>57351</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2908,21 +2889,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2932,10 +2913,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585818</v>
+        <v>585866</v>
       </c>
       <c r="R21" t="n">
-        <v>7084786</v>
+        <v>7084575</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,12 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3009,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346622</v>
+        <v>121347308</v>
       </c>
       <c r="B22" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3021,38 +2997,52 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585815</v>
+        <v>585988</v>
       </c>
       <c r="R22" t="n">
-        <v>7084624</v>
+        <v>7084426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3084,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3094,7 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,22 +3099,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346437</v>
+        <v>121347517</v>
       </c>
       <c r="B23" t="n">
-        <v>90728</v>
+        <v>78607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3137,21 +3127,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3161,10 +3151,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585813</v>
+        <v>585965</v>
       </c>
       <c r="R23" t="n">
-        <v>7084694</v>
+        <v>7084448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3196,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3206,7 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347327</v>
+        <v>121347310</v>
       </c>
       <c r="B24" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3273,10 +3263,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586037</v>
+        <v>585983</v>
       </c>
       <c r="R24" t="n">
-        <v>7084389</v>
+        <v>7084425</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3308,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3318,7 +3308,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346096</v>
+        <v>121346437</v>
       </c>
       <c r="B25" t="n">
-        <v>78604</v>
+        <v>90731</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,21 +3351,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3385,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585791</v>
+        <v>585813</v>
       </c>
       <c r="R25" t="n">
-        <v>7084728</v>
+        <v>7084694</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3420,7 +3410,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3430,7 +3420,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3457,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346594</v>
+        <v>121346558</v>
       </c>
       <c r="B26" t="n">
-        <v>98095</v>
+        <v>78607</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3469,42 +3459,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585801</v>
+        <v>585813</v>
       </c>
       <c r="R26" t="n">
-        <v>7084642</v>
+        <v>7084662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3536,7 +3522,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3546,7 +3532,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3573,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346090</v>
+        <v>121346703</v>
       </c>
       <c r="B27" t="n">
-        <v>78604</v>
+        <v>98098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3585,38 +3571,52 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585825</v>
+        <v>585863</v>
       </c>
       <c r="R27" t="n">
-        <v>7084709</v>
+        <v>7084578</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3685,10 +3685,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346034</v>
+        <v>121347327</v>
       </c>
       <c r="B28" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585813</v>
+        <v>586037</v>
       </c>
       <c r="R28" t="n">
-        <v>7084756</v>
+        <v>7084389</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,22 +3785,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346810</v>
+        <v>121347731</v>
       </c>
       <c r="B29" t="n">
-        <v>97049</v>
+        <v>78607</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,25 +3809,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585874</v>
+        <v>585899</v>
       </c>
       <c r="R29" t="n">
-        <v>7084559</v>
+        <v>7084492</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121346543</v>
+        <v>121347308</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -710,7 +710,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585822</v>
+        <v>585988</v>
       </c>
       <c r="R2" t="n">
-        <v>7084651</v>
+        <v>7084426</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347537</v>
+        <v>121347298</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,27 +817,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -836,13 +855,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585943</v>
+        <v>585969</v>
       </c>
       <c r="R3" t="n">
-        <v>7084462</v>
+        <v>7084411</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +890,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +900,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346096</v>
+        <v>121346437</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>90731</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,21 +943,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585791</v>
+        <v>585813</v>
       </c>
       <c r="R4" t="n">
-        <v>7084728</v>
+        <v>7084694</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1132,10 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346810</v>
+        <v>121346703</v>
       </c>
       <c r="B6" t="n">
-        <v>97052</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,38 +1163,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585874</v>
+        <v>585863</v>
       </c>
       <c r="R6" t="n">
-        <v>7084559</v>
+        <v>7084578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1207,7 +1240,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1250,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,7 +1277,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347495</v>
+        <v>121347310</v>
       </c>
       <c r="B7" t="n">
         <v>78607</v>
@@ -1284,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586092</v>
+        <v>585983</v>
       </c>
       <c r="R7" t="n">
-        <v>7084449</v>
+        <v>7084425</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,7 +1362,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,7 +1389,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346622</v>
+        <v>121347731</v>
       </c>
       <c r="B8" t="n">
         <v>78607</v>
@@ -1396,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585815</v>
+        <v>585899</v>
       </c>
       <c r="R8" t="n">
-        <v>7084624</v>
+        <v>7084492</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1441,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,10 +1501,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347155</v>
+        <v>121346576</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>90713</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1480,52 +1513,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585879</v>
+        <v>585803</v>
       </c>
       <c r="R9" t="n">
-        <v>7084451</v>
+        <v>7084658</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1557,7 +1576,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1567,7 +1586,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,22 +1601,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346000</v>
+        <v>121346594</v>
       </c>
       <c r="B10" t="n">
-        <v>57354</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,38 +1625,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585818</v>
+        <v>585801</v>
       </c>
       <c r="R10" t="n">
-        <v>7084786</v>
+        <v>7084642</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,12 +1702,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347298</v>
+        <v>121347537</v>
       </c>
       <c r="B11" t="n">
-        <v>57507</v>
+        <v>57370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,36 +1745,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1765,13 +1774,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585969</v>
+        <v>585943</v>
       </c>
       <c r="R11" t="n">
-        <v>7084411</v>
+        <v>7084462</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1800,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,7 +1819,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1837,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346576</v>
+        <v>121347155</v>
       </c>
       <c r="B12" t="n">
-        <v>90713</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,38 +1858,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585803</v>
+        <v>585879</v>
       </c>
       <c r="R12" t="n">
-        <v>7084658</v>
+        <v>7084451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1945,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1937,19 +1960,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346034</v>
+        <v>121347517</v>
       </c>
       <c r="B13" t="n">
         <v>78607</v>
@@ -1989,10 +2012,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585813</v>
+        <v>585965</v>
       </c>
       <c r="R13" t="n">
-        <v>7084756</v>
+        <v>7084448</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,7 +2047,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +2057,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +2084,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346090</v>
+        <v>121347511</v>
       </c>
       <c r="B14" t="n">
         <v>78607</v>
@@ -2101,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585825</v>
+        <v>586046</v>
       </c>
       <c r="R14" t="n">
-        <v>7084709</v>
+        <v>7084490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,22 +2184,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347019</v>
+        <v>121346090</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2185,42 +2208,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585857</v>
+        <v>585825</v>
       </c>
       <c r="R15" t="n">
-        <v>7084489</v>
+        <v>7084709</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2271,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2281,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,19 +2296,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346522</v>
+        <v>121347424</v>
       </c>
       <c r="B16" t="n">
         <v>57354</v>
@@ -2330,14 +2349,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585825</v>
+        <v>586076</v>
       </c>
       <c r="R16" t="n">
-        <v>7084654</v>
+        <v>7084414</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2388,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,12 +2398,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2411,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346594</v>
+        <v>121346622</v>
       </c>
       <c r="B17" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,42 +2442,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585801</v>
+        <v>585815</v>
       </c>
       <c r="R17" t="n">
-        <v>7084642</v>
+        <v>7084624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2490,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2500,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,7 +2542,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347424</v>
+        <v>121346522</v>
       </c>
       <c r="B18" t="n">
         <v>57354</v>
@@ -2568,14 +2583,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>586076</v>
+        <v>585825</v>
       </c>
       <c r="R18" t="n">
-        <v>7084414</v>
+        <v>7084654</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2607,7 +2622,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2617,12 +2632,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2649,7 +2664,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347511</v>
+        <v>121346709</v>
       </c>
       <c r="B19" t="n">
         <v>78607</v>
@@ -2689,10 +2704,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>586046</v>
+        <v>585866</v>
       </c>
       <c r="R19" t="n">
-        <v>7084490</v>
+        <v>7084575</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2724,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2734,7 +2749,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2761,10 +2776,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347539</v>
+        <v>121346543</v>
       </c>
       <c r="B20" t="n">
-        <v>78607</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2773,38 +2788,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585948</v>
+        <v>585822</v>
       </c>
       <c r="R20" t="n">
-        <v>7084466</v>
+        <v>7084651</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2836,7 +2855,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2846,7 +2865,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2873,7 +2892,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346709</v>
+        <v>121346096</v>
       </c>
       <c r="B21" t="n">
         <v>78607</v>
@@ -2913,10 +2932,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585866</v>
+        <v>585791</v>
       </c>
       <c r="R21" t="n">
-        <v>7084575</v>
+        <v>7084728</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2948,7 +2967,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2977,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,10 +3004,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347308</v>
+        <v>121347539</v>
       </c>
       <c r="B22" t="n">
-        <v>98098</v>
+        <v>78607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,52 +3016,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585988</v>
+        <v>585948</v>
       </c>
       <c r="R22" t="n">
-        <v>7084426</v>
+        <v>7084466</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,19 +3104,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347517</v>
+        <v>121347327</v>
       </c>
       <c r="B23" t="n">
         <v>78607</v>
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585965</v>
+        <v>586037</v>
       </c>
       <c r="R23" t="n">
-        <v>7084448</v>
+        <v>7084389</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,7 +3201,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3211,19 +3216,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347310</v>
+        <v>121347495</v>
       </c>
       <c r="B24" t="n">
         <v>78607</v>
@@ -3263,10 +3268,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585983</v>
+        <v>586092</v>
       </c>
       <c r="R24" t="n">
-        <v>7084425</v>
+        <v>7084449</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3298,7 +3303,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3308,7 +3313,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,10 +3340,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346437</v>
+        <v>121346558</v>
       </c>
       <c r="B25" t="n">
-        <v>90731</v>
+        <v>78607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3351,21 +3356,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3378,7 +3383,7 @@
         <v>585813</v>
       </c>
       <c r="R25" t="n">
-        <v>7084694</v>
+        <v>7084662</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3410,7 +3415,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3420,7 +3425,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3447,10 +3452,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346558</v>
+        <v>121346000</v>
       </c>
       <c r="B26" t="n">
-        <v>78607</v>
+        <v>57354</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3463,21 +3468,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3487,10 +3492,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585813</v>
+        <v>585818</v>
       </c>
       <c r="R26" t="n">
-        <v>7084662</v>
+        <v>7084786</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3522,7 +3527,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3532,7 +3537,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3559,7 +3569,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346703</v>
+        <v>121347019</v>
       </c>
       <c r="B27" t="n">
         <v>98098</v>
@@ -3594,17 +3604,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585863</v>
+        <v>585857</v>
       </c>
       <c r="R27" t="n">
-        <v>7084578</v>
+        <v>7084489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,22 +3673,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347327</v>
+        <v>121346810</v>
       </c>
       <c r="B28" t="n">
-        <v>78607</v>
+        <v>97052</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,25 +3697,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586037</v>
+        <v>585874</v>
       </c>
       <c r="R28" t="n">
-        <v>7084389</v>
+        <v>7084559</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,19 +3785,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347731</v>
+        <v>121346034</v>
       </c>
       <c r="B29" t="n">
         <v>78607</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585899</v>
+        <v>585813</v>
       </c>
       <c r="R29" t="n">
-        <v>7084492</v>
+        <v>7084756</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346594</v>
+        <v>121347537</v>
       </c>
       <c r="B10" t="n">
-        <v>98098</v>
+        <v>57370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,42 +1625,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585801</v>
+        <v>585943</v>
       </c>
       <c r="R10" t="n">
-        <v>7084642</v>
+        <v>7084462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1693,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,7 +1703,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,22 +1718,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347537</v>
+        <v>121346594</v>
       </c>
       <c r="B11" t="n">
-        <v>57370</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,43 +1742,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585943</v>
+        <v>585801</v>
       </c>
       <c r="R11" t="n">
-        <v>7084462</v>
+        <v>7084642</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,12 +1834,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121347308</v>
+        <v>121347495</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585988</v>
+        <v>586092</v>
       </c>
       <c r="R2" t="n">
-        <v>7084426</v>
+        <v>7084449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347298</v>
+        <v>121347155</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>98104</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,55 +799,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585969</v>
+        <v>585879</v>
       </c>
       <c r="R3" t="n">
-        <v>7084411</v>
+        <v>7084451</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -900,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,10 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346437</v>
+        <v>121346576</v>
       </c>
       <c r="B4" t="n">
-        <v>90731</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585813</v>
+        <v>585803</v>
       </c>
       <c r="R4" t="n">
-        <v>7084694</v>
+        <v>7084658</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1012,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346435</v>
+        <v>121346522</v>
       </c>
       <c r="B5" t="n">
-        <v>78607</v>
+        <v>57355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1041,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585819</v>
+        <v>585825</v>
       </c>
       <c r="R5" t="n">
-        <v>7084684</v>
+        <v>7084654</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1124,7 +1115,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346703</v>
+        <v>121346543</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,17 +1182,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1205,10 +1191,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585863</v>
+        <v>585822</v>
       </c>
       <c r="R6" t="n">
-        <v>7084578</v>
+        <v>7084651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,7 +1226,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1250,7 +1236,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,22 +1251,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347310</v>
+        <v>121346810</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
+        <v>97058</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,25 +1275,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1317,10 +1303,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585983</v>
+        <v>585874</v>
       </c>
       <c r="R7" t="n">
-        <v>7084425</v>
+        <v>7084559</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,7 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347731</v>
+        <v>121347517</v>
       </c>
       <c r="B8" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1429,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585899</v>
+        <v>585965</v>
       </c>
       <c r="R8" t="n">
-        <v>7084492</v>
+        <v>7084448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,22 +1475,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346576</v>
+        <v>121346435</v>
       </c>
       <c r="B9" t="n">
-        <v>90713</v>
+        <v>78608</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1517,21 +1503,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1541,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585803</v>
+        <v>585819</v>
       </c>
       <c r="R9" t="n">
-        <v>7084658</v>
+        <v>7084684</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1576,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1586,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,22 +1587,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347537</v>
+        <v>121346034</v>
       </c>
       <c r="B10" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,39 +1615,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585943</v>
+        <v>585813</v>
       </c>
       <c r="R10" t="n">
-        <v>7084462</v>
+        <v>7084756</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1693,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1703,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,10 +1711,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346594</v>
+        <v>121346090</v>
       </c>
       <c r="B11" t="n">
-        <v>98098</v>
+        <v>78608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,42 +1723,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585801</v>
+        <v>585825</v>
       </c>
       <c r="R11" t="n">
-        <v>7084642</v>
+        <v>7084709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1809,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1819,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,22 +1811,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347155</v>
+        <v>121347019</v>
       </c>
       <c r="B12" t="n">
-        <v>98098</v>
+        <v>98104</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,17 +1858,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1900,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585879</v>
+        <v>585857</v>
       </c>
       <c r="R12" t="n">
-        <v>7084451</v>
+        <v>7084489</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1945,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1960,22 +1927,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347517</v>
+        <v>121346558</v>
       </c>
       <c r="B13" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585965</v>
+        <v>585813</v>
       </c>
       <c r="R13" t="n">
-        <v>7084448</v>
+        <v>7084662</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,22 +2039,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347511</v>
+        <v>121347731</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586046</v>
+        <v>585899</v>
       </c>
       <c r="R14" t="n">
-        <v>7084490</v>
+        <v>7084492</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346090</v>
+        <v>121347511</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,10 +2203,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585825</v>
+        <v>586046</v>
       </c>
       <c r="R15" t="n">
-        <v>7084709</v>
+        <v>7084490</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2271,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2281,7 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2296,22 +2263,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347424</v>
+        <v>121346594</v>
       </c>
       <c r="B16" t="n">
-        <v>57354</v>
+        <v>98104</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2320,43 +2287,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>586076</v>
+        <v>585801</v>
       </c>
       <c r="R16" t="n">
-        <v>7084414</v>
+        <v>7084642</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2388,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2398,12 +2364,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2418,22 +2379,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346622</v>
+        <v>121347327</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2470,10 +2431,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585815</v>
+        <v>586037</v>
       </c>
       <c r="R17" t="n">
-        <v>7084624</v>
+        <v>7084389</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,7 +2466,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2515,7 +2476,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,10 +2503,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346522</v>
+        <v>121346096</v>
       </c>
       <c r="B18" t="n">
-        <v>57354</v>
+        <v>78608</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2558,39 +2519,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585825</v>
+        <v>585791</v>
       </c>
       <c r="R18" t="n">
-        <v>7084654</v>
+        <v>7084728</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2622,7 +2578,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2632,12 +2588,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2652,22 +2603,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346709</v>
+        <v>121346622</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2704,10 +2655,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585866</v>
+        <v>585815</v>
       </c>
       <c r="R19" t="n">
-        <v>7084575</v>
+        <v>7084624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2739,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2776,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346543</v>
+        <v>121347298</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>57508</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2788,45 +2739,55 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585822</v>
+        <v>585969</v>
       </c>
       <c r="R20" t="n">
-        <v>7084651</v>
+        <v>7084411</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2855,7 +2816,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2865,7 +2826,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2880,22 +2841,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346096</v>
+        <v>121347308</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2904,38 +2865,52 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585791</v>
+        <v>585988</v>
       </c>
       <c r="R21" t="n">
-        <v>7084728</v>
+        <v>7084426</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2967,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,7 +2952,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2992,22 +2967,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347539</v>
+        <v>121347310</v>
       </c>
       <c r="B22" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3044,10 +3019,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585948</v>
+        <v>585983</v>
       </c>
       <c r="R22" t="n">
-        <v>7084466</v>
+        <v>7084425</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3079,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3064,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3116,10 +3091,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347327</v>
+        <v>121346709</v>
       </c>
       <c r="B23" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3156,10 +3131,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>586037</v>
+        <v>585866</v>
       </c>
       <c r="R23" t="n">
-        <v>7084389</v>
+        <v>7084575</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3191,7 +3166,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,7 +3176,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3228,10 +3203,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347495</v>
+        <v>121347537</v>
       </c>
       <c r="B24" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3244,34 +3219,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>586092</v>
+        <v>585943</v>
       </c>
       <c r="R24" t="n">
-        <v>7084449</v>
+        <v>7084462</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3303,7 +3283,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3293,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3328,22 +3308,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346558</v>
+        <v>121347539</v>
       </c>
       <c r="B25" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3380,10 +3360,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585813</v>
+        <v>585948</v>
       </c>
       <c r="R25" t="n">
-        <v>7084662</v>
+        <v>7084466</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3415,7 +3395,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3425,7 +3405,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3452,10 +3432,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346000</v>
+        <v>121346437</v>
       </c>
       <c r="B26" t="n">
-        <v>57354</v>
+        <v>90737</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3468,21 +3448,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3492,10 +3472,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585818</v>
+        <v>585813</v>
       </c>
       <c r="R26" t="n">
-        <v>7084786</v>
+        <v>7084694</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3527,7 +3507,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3537,12 +3517,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3569,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347019</v>
+        <v>121347424</v>
       </c>
       <c r="B27" t="n">
-        <v>98098</v>
+        <v>57355</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,42 +3556,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585857</v>
+        <v>586076</v>
       </c>
       <c r="R27" t="n">
-        <v>7084489</v>
+        <v>7084414</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,7 +3624,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3634,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,22 +3654,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346810</v>
+        <v>121346000</v>
       </c>
       <c r="B28" t="n">
-        <v>97052</v>
+        <v>57355</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,25 +3678,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3725,10 +3706,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585874</v>
+        <v>585818</v>
       </c>
       <c r="R28" t="n">
-        <v>7084559</v>
+        <v>7084786</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3741,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3751,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,22 +3771,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346034</v>
+        <v>121346703</v>
       </c>
       <c r="B29" t="n">
-        <v>78607</v>
+        <v>98104</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,38 +3795,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585813</v>
+        <v>585863</v>
       </c>
       <c r="R29" t="n">
-        <v>7084756</v>
+        <v>7084578</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121347495</v>
+        <v>121347155</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>98104</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>586092</v>
+        <v>585879</v>
       </c>
       <c r="R2" t="n">
-        <v>7084449</v>
+        <v>7084451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +789,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347155</v>
+        <v>121347495</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>78608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,52 +813,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585879</v>
+        <v>586092</v>
       </c>
       <c r="R3" t="n">
-        <v>7084451</v>
+        <v>7084449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,12 +901,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121347155</v>
+        <v>121346810</v>
       </c>
       <c r="B2" t="n">
-        <v>98104</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585879</v>
+        <v>585874</v>
       </c>
       <c r="R2" t="n">
-        <v>7084451</v>
+        <v>7084559</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347495</v>
+        <v>121346576</v>
       </c>
       <c r="B3" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -841,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>586092</v>
+        <v>585803</v>
       </c>
       <c r="R3" t="n">
-        <v>7084449</v>
+        <v>7084658</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346576</v>
+        <v>121347155</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +911,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585803</v>
+        <v>585879</v>
       </c>
       <c r="R4" t="n">
-        <v>7084658</v>
+        <v>7084451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346522</v>
+        <v>121347539</v>
       </c>
       <c r="B5" t="n">
-        <v>57355</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,39 +1041,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585825</v>
+        <v>585948</v>
       </c>
       <c r="R5" t="n">
-        <v>7084654</v>
+        <v>7084466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346543</v>
+        <v>121346034</v>
       </c>
       <c r="B6" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,42 +1149,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585822</v>
+        <v>585813</v>
       </c>
       <c r="R6" t="n">
-        <v>7084651</v>
+        <v>7084756</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1236,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,22 +1237,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346810</v>
+        <v>121346709</v>
       </c>
       <c r="B7" t="n">
-        <v>97058</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,25 +1261,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1303,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585874</v>
+        <v>585866</v>
       </c>
       <c r="R7" t="n">
-        <v>7084559</v>
+        <v>7084575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1349,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347517</v>
+        <v>121346622</v>
       </c>
       <c r="B8" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1415,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585965</v>
+        <v>585815</v>
       </c>
       <c r="R8" t="n">
-        <v>7084448</v>
+        <v>7084624</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,22 +1461,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346435</v>
+        <v>121347731</v>
       </c>
       <c r="B9" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1527,10 +1513,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585819</v>
+        <v>585899</v>
       </c>
       <c r="R9" t="n">
-        <v>7084684</v>
+        <v>7084492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1562,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1572,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1573,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346034</v>
+        <v>121347537</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,34 +1601,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585813</v>
+        <v>585943</v>
       </c>
       <c r="R10" t="n">
-        <v>7084756</v>
+        <v>7084462</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1674,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1684,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1711,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346090</v>
+        <v>121347298</v>
       </c>
       <c r="B11" t="n">
-        <v>78608</v>
+        <v>57509</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1727,37 +1718,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585825</v>
+        <v>585969</v>
       </c>
       <c r="R11" t="n">
-        <v>7084709</v>
+        <v>7084411</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,7 +1791,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1796,7 +1801,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1823,10 +1828,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347019</v>
+        <v>121347327</v>
       </c>
       <c r="B12" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,42 +1840,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585857</v>
+        <v>586037</v>
       </c>
       <c r="R12" t="n">
-        <v>7084489</v>
+        <v>7084389</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1913,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346558</v>
+        <v>121346096</v>
       </c>
       <c r="B13" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1979,10 +1980,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585813</v>
+        <v>585791</v>
       </c>
       <c r="R13" t="n">
-        <v>7084662</v>
+        <v>7084728</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2052,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347731</v>
+        <v>121346543</v>
       </c>
       <c r="B14" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,38 +2064,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585899</v>
+        <v>585822</v>
       </c>
       <c r="R14" t="n">
-        <v>7084492</v>
+        <v>7084651</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2131,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2141,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347511</v>
+        <v>121346435</v>
       </c>
       <c r="B15" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>586046</v>
+        <v>585819</v>
       </c>
       <c r="R15" t="n">
-        <v>7084490</v>
+        <v>7084684</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,22 +2268,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346594</v>
+        <v>121346703</v>
       </c>
       <c r="B16" t="n">
-        <v>98104</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,7 +2315,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2319,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585801</v>
+        <v>585863</v>
       </c>
       <c r="R16" t="n">
-        <v>7084642</v>
+        <v>7084578</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2379,22 +2394,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347327</v>
+        <v>121346090</v>
       </c>
       <c r="B17" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,10 +2446,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>586037</v>
+        <v>585825</v>
       </c>
       <c r="R17" t="n">
-        <v>7084389</v>
+        <v>7084709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2466,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2476,7 +2491,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2491,22 +2506,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346096</v>
+        <v>121347019</v>
       </c>
       <c r="B18" t="n">
-        <v>78608</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2515,38 +2530,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585791</v>
+        <v>585857</v>
       </c>
       <c r="R18" t="n">
-        <v>7084728</v>
+        <v>7084489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2578,7 +2597,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2588,7 +2607,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2615,10 +2634,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346622</v>
+        <v>121346558</v>
       </c>
       <c r="B19" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2655,10 +2674,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585815</v>
+        <v>585813</v>
       </c>
       <c r="R19" t="n">
-        <v>7084624</v>
+        <v>7084662</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2709,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2719,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2746,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347298</v>
+        <v>121347511</v>
       </c>
       <c r="B20" t="n">
-        <v>57508</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2743,51 +2762,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585969</v>
+        <v>586046</v>
       </c>
       <c r="R20" t="n">
-        <v>7084411</v>
+        <v>7084490</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2816,7 +2821,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2826,7 +2831,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2841,22 +2846,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347308</v>
+        <v>121347424</v>
       </c>
       <c r="B21" t="n">
-        <v>98104</v>
+        <v>57356</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2865,52 +2870,43 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585988</v>
+        <v>586076</v>
       </c>
       <c r="R21" t="n">
-        <v>7084426</v>
+        <v>7084414</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2942,7 +2938,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,7 +2948,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,10 +2980,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347310</v>
+        <v>121347517</v>
       </c>
       <c r="B22" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,10 +3020,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585983</v>
+        <v>585965</v>
       </c>
       <c r="R22" t="n">
-        <v>7084425</v>
+        <v>7084448</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3055,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,7 +3065,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3079,22 +3080,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346709</v>
+        <v>121346000</v>
       </c>
       <c r="B23" t="n">
-        <v>78608</v>
+        <v>57356</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3107,21 +3108,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3131,10 +3132,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585866</v>
+        <v>585818</v>
       </c>
       <c r="R23" t="n">
-        <v>7084575</v>
+        <v>7084786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3166,7 +3167,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3176,7 +3177,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3203,10 +3209,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347537</v>
+        <v>121346522</v>
       </c>
       <c r="B24" t="n">
-        <v>57371</v>
+        <v>57356</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3219,16 +3225,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3244,14 +3250,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585943</v>
+        <v>585825</v>
       </c>
       <c r="R24" t="n">
-        <v>7084462</v>
+        <v>7084654</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3283,7 +3289,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3293,7 +3299,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3320,10 +3331,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347539</v>
+        <v>121347310</v>
       </c>
       <c r="B25" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3360,10 +3371,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585948</v>
+        <v>585983</v>
       </c>
       <c r="R25" t="n">
-        <v>7084466</v>
+        <v>7084425</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3395,7 +3406,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3405,7 +3416,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3432,10 +3443,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346437</v>
+        <v>121347308</v>
       </c>
       <c r="B26" t="n">
-        <v>90737</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3444,38 +3455,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585813</v>
+        <v>585988</v>
       </c>
       <c r="R26" t="n">
-        <v>7084694</v>
+        <v>7084426</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3507,7 +3532,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3517,7 +3542,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3532,22 +3557,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347424</v>
+        <v>121346594</v>
       </c>
       <c r="B27" t="n">
-        <v>57355</v>
+        <v>98105</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3556,43 +3581,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>586076</v>
+        <v>585801</v>
       </c>
       <c r="R27" t="n">
-        <v>7084414</v>
+        <v>7084642</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3624,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3634,12 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3654,22 +3673,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346000</v>
+        <v>121346437</v>
       </c>
       <c r="B28" t="n">
-        <v>57355</v>
+        <v>90738</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3682,21 +3701,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3706,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585818</v>
+        <v>585813</v>
       </c>
       <c r="R28" t="n">
-        <v>7084786</v>
+        <v>7084694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3741,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3751,12 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3783,10 +3797,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346703</v>
+        <v>121347495</v>
       </c>
       <c r="B29" t="n">
-        <v>98104</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3795,52 +3809,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585863</v>
+        <v>586092</v>
       </c>
       <c r="R29" t="n">
-        <v>7084578</v>
+        <v>7084449</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121346810</v>
+        <v>121346703</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>98105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585874</v>
+        <v>585863</v>
       </c>
       <c r="R2" t="n">
-        <v>7084559</v>
+        <v>7084578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346576</v>
+        <v>121346034</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +817,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585803</v>
+        <v>585813</v>
       </c>
       <c r="R3" t="n">
-        <v>7084658</v>
+        <v>7084756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +901,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347155</v>
+        <v>121346622</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,52 +925,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585879</v>
+        <v>585815</v>
       </c>
       <c r="R4" t="n">
-        <v>7084451</v>
+        <v>7084624</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,19 +1013,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347539</v>
+        <v>121347731</v>
       </c>
       <c r="B5" t="n">
         <v>78609</v>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585948</v>
+        <v>585899</v>
       </c>
       <c r="R5" t="n">
-        <v>7084466</v>
+        <v>7084492</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346034</v>
+        <v>121346096</v>
       </c>
       <c r="B6" t="n">
         <v>78609</v>
@@ -1177,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585813</v>
+        <v>585791</v>
       </c>
       <c r="R6" t="n">
-        <v>7084756</v>
+        <v>7084728</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,19 +1237,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346709</v>
+        <v>121346558</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585866</v>
+        <v>585813</v>
       </c>
       <c r="R7" t="n">
-        <v>7084575</v>
+        <v>7084662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1361,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346622</v>
+        <v>121347327</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585815</v>
+        <v>586037</v>
       </c>
       <c r="R8" t="n">
-        <v>7084624</v>
+        <v>7084389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347731</v>
+        <v>121346594</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,38 +1485,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585899</v>
+        <v>585801</v>
       </c>
       <c r="R9" t="n">
-        <v>7084492</v>
+        <v>7084642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1552,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1562,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1589,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347537</v>
+        <v>121347517</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,39 +1605,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585943</v>
+        <v>585965</v>
       </c>
       <c r="R10" t="n">
-        <v>7084462</v>
+        <v>7084448</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1665,7 +1664,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1674,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1828,7 +1827,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347327</v>
+        <v>121346090</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1868,10 +1867,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>586037</v>
+        <v>585825</v>
       </c>
       <c r="R12" t="n">
-        <v>7084389</v>
+        <v>7084709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1903,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1913,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,19 +1927,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346096</v>
+        <v>121347310</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1980,10 +1979,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585791</v>
+        <v>585983</v>
       </c>
       <c r="R13" t="n">
-        <v>7084728</v>
+        <v>7084425</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2015,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2025,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2052,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346543</v>
+        <v>121346000</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,42 +2063,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585822</v>
+        <v>585818</v>
       </c>
       <c r="R14" t="n">
-        <v>7084651</v>
+        <v>7084786</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2131,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2141,7 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2168,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346435</v>
+        <v>121347019</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2180,38 +2180,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585819</v>
+        <v>585857</v>
       </c>
       <c r="R15" t="n">
-        <v>7084684</v>
+        <v>7084489</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,19 +2272,19 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346703</v>
+        <v>121347155</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2315,7 +2319,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2334,10 +2338,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585863</v>
+        <v>585879</v>
       </c>
       <c r="R16" t="n">
-        <v>7084578</v>
+        <v>7084451</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2373,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2383,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2410,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346090</v>
+        <v>121346437</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,21 +2426,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2446,10 +2450,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585825</v>
+        <v>585813</v>
       </c>
       <c r="R17" t="n">
-        <v>7084709</v>
+        <v>7084694</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2485,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,7 +2495,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2506,22 +2510,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347019</v>
+        <v>121346709</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,42 +2534,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585857</v>
+        <v>585866</v>
       </c>
       <c r="R18" t="n">
-        <v>7084489</v>
+        <v>7084575</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,7 +2634,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346558</v>
+        <v>121346435</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2674,10 +2674,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585813</v>
+        <v>585819</v>
       </c>
       <c r="R19" t="n">
-        <v>7084662</v>
+        <v>7084684</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,22 +2734,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347511</v>
+        <v>121346543</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,38 +2758,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586046</v>
+        <v>585822</v>
       </c>
       <c r="R20" t="n">
-        <v>7084490</v>
+        <v>7084651</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2821,7 +2825,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2831,7 +2835,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2858,10 +2862,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347424</v>
+        <v>121346810</v>
       </c>
       <c r="B21" t="n">
-        <v>57356</v>
+        <v>97059</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2870,43 +2874,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586076</v>
+        <v>585874</v>
       </c>
       <c r="R21" t="n">
-        <v>7084414</v>
+        <v>7084559</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2937,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,12 +2947,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2980,10 +2974,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347517</v>
+        <v>121347424</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2996,34 +2990,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585965</v>
+        <v>586076</v>
       </c>
       <c r="R22" t="n">
-        <v>7084448</v>
+        <v>7084414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3055,7 +3054,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3065,7 +3064,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3092,10 +3096,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346000</v>
+        <v>121346576</v>
       </c>
       <c r="B23" t="n">
-        <v>57356</v>
+        <v>90720</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3108,21 +3112,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3132,10 +3136,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585818</v>
+        <v>585803</v>
       </c>
       <c r="R23" t="n">
-        <v>7084786</v>
+        <v>7084658</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3167,7 +3171,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3177,12 +3181,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3331,7 +3330,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347310</v>
+        <v>121347495</v>
       </c>
       <c r="B25" t="n">
         <v>78609</v>
@@ -3371,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585983</v>
+        <v>586092</v>
       </c>
       <c r="R25" t="n">
-        <v>7084425</v>
+        <v>7084449</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3406,7 +3405,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3416,7 +3415,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3443,10 +3442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347308</v>
+        <v>121347511</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3455,52 +3454,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585988</v>
+        <v>586046</v>
       </c>
       <c r="R26" t="n">
-        <v>7084426</v>
+        <v>7084490</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3532,7 +3517,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3542,7 +3527,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3557,22 +3542,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346594</v>
+        <v>121347537</v>
       </c>
       <c r="B27" t="n">
-        <v>98105</v>
+        <v>57372</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3581,42 +3566,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585801</v>
+        <v>585943</v>
       </c>
       <c r="R27" t="n">
-        <v>7084642</v>
+        <v>7084462</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,7 +3634,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3644,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,22 +3659,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346437</v>
+        <v>121347308</v>
       </c>
       <c r="B28" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3697,38 +3683,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585813</v>
+        <v>585988</v>
       </c>
       <c r="R28" t="n">
-        <v>7084694</v>
+        <v>7084426</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,19 +3785,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347495</v>
+        <v>121347539</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>586092</v>
+        <v>585948</v>
       </c>
       <c r="R29" t="n">
-        <v>7084449</v>
+        <v>7084466</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121346703</v>
+        <v>121346576</v>
       </c>
       <c r="B2" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585863</v>
+        <v>585803</v>
       </c>
       <c r="R2" t="n">
-        <v>7084578</v>
+        <v>7084658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346034</v>
+        <v>121346622</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -841,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585813</v>
+        <v>585815</v>
       </c>
       <c r="R3" t="n">
-        <v>7084756</v>
+        <v>7084624</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,22 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346622</v>
+        <v>121347308</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,38 +911,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585815</v>
+        <v>585988</v>
       </c>
       <c r="R4" t="n">
-        <v>7084624</v>
+        <v>7084426</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347731</v>
+        <v>121347537</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,34 +1041,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585899</v>
+        <v>585943</v>
       </c>
       <c r="R5" t="n">
-        <v>7084492</v>
+        <v>7084462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346096</v>
+        <v>121346703</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,38 +1154,52 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585791</v>
+        <v>585863</v>
       </c>
       <c r="R6" t="n">
-        <v>7084728</v>
+        <v>7084578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1231,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1241,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,19 +1256,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346558</v>
+        <v>121347731</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1289,10 +1308,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585813</v>
+        <v>585899</v>
       </c>
       <c r="R7" t="n">
-        <v>7084662</v>
+        <v>7084492</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1343,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1353,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,7 +1380,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347327</v>
+        <v>121346096</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1401,10 +1420,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586037</v>
+        <v>585791</v>
       </c>
       <c r="R8" t="n">
-        <v>7084389</v>
+        <v>7084728</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1436,7 +1455,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1465,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1492,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346594</v>
+        <v>121346090</v>
       </c>
       <c r="B9" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,42 +1504,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585801</v>
+        <v>585825</v>
       </c>
       <c r="R9" t="n">
-        <v>7084642</v>
+        <v>7084709</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1577,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,22 +1592,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347517</v>
+        <v>121346000</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,21 +1620,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1644,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585965</v>
+        <v>585818</v>
       </c>
       <c r="R10" t="n">
-        <v>7084448</v>
+        <v>7084786</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1679,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,7 +1689,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,22 +1709,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347298</v>
+        <v>121346034</v>
       </c>
       <c r="B11" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,51 +1737,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585969</v>
+        <v>585813</v>
       </c>
       <c r="R11" t="n">
-        <v>7084411</v>
+        <v>7084756</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1790,7 +1796,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1806,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,10 +1833,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346090</v>
+        <v>121347298</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,37 +1849,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585825</v>
+        <v>585969</v>
       </c>
       <c r="R12" t="n">
-        <v>7084709</v>
+        <v>7084411</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,7 +1959,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347310</v>
+        <v>121347511</v>
       </c>
       <c r="B13" t="n">
         <v>78609</v>
@@ -1979,10 +1999,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585983</v>
+        <v>586046</v>
       </c>
       <c r="R13" t="n">
-        <v>7084425</v>
+        <v>7084490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2044,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,7 +2071,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346000</v>
+        <v>121347424</v>
       </c>
       <c r="B14" t="n">
         <v>57356</v>
@@ -2085,16 +2105,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585818</v>
+        <v>586076</v>
       </c>
       <c r="R14" t="n">
-        <v>7084786</v>
+        <v>7084414</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2151,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2161,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,19 +2181,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347019</v>
+        <v>121346594</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2203,7 +2228,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2237,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585857</v>
+        <v>585801</v>
       </c>
       <c r="R15" t="n">
-        <v>7084489</v>
+        <v>7084642</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2272,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2282,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2284,10 +2309,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347155</v>
+        <v>121346522</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,40 +2321,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2338,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585879</v>
+        <v>585825</v>
       </c>
       <c r="R16" t="n">
-        <v>7084451</v>
+        <v>7084654</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2373,7 +2389,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2383,7 +2399,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2410,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346437</v>
+        <v>121346543</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,38 +2443,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585813</v>
+        <v>585822</v>
       </c>
       <c r="R17" t="n">
-        <v>7084694</v>
+        <v>7084651</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2485,7 +2510,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2495,7 +2520,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,10 +2547,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346709</v>
+        <v>121347019</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2534,38 +2559,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585866</v>
+        <v>585857</v>
       </c>
       <c r="R18" t="n">
-        <v>7084575</v>
+        <v>7084489</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2597,7 +2626,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2607,7 +2636,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2634,7 +2663,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346435</v>
+        <v>121347539</v>
       </c>
       <c r="B19" t="n">
         <v>78609</v>
@@ -2674,10 +2703,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585819</v>
+        <v>585948</v>
       </c>
       <c r="R19" t="n">
-        <v>7084684</v>
+        <v>7084466</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2709,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2719,7 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,22 +2763,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346543</v>
+        <v>121347327</v>
       </c>
       <c r="B20" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,42 +2787,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585822</v>
+        <v>586037</v>
       </c>
       <c r="R20" t="n">
-        <v>7084651</v>
+        <v>7084389</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2825,7 +2850,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2835,7 +2860,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,10 +2887,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346810</v>
+        <v>121347310</v>
       </c>
       <c r="B21" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2874,25 +2899,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2902,10 +2927,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585874</v>
+        <v>585983</v>
       </c>
       <c r="R21" t="n">
-        <v>7084559</v>
+        <v>7084425</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2937,7 +2962,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2947,7 +2972,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2962,22 +2987,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347424</v>
+        <v>121347495</v>
       </c>
       <c r="B22" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2990,39 +3015,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586076</v>
+        <v>586092</v>
       </c>
       <c r="R22" t="n">
-        <v>7084414</v>
+        <v>7084449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3054,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3064,12 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3084,22 +3099,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346576</v>
+        <v>121346435</v>
       </c>
       <c r="B23" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,21 +3127,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3136,10 +3151,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585803</v>
+        <v>585819</v>
       </c>
       <c r="R23" t="n">
-        <v>7084658</v>
+        <v>7084684</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3171,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3181,7 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121346522</v>
+        <v>121347155</v>
       </c>
       <c r="B24" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3220,31 +3235,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3253,10 +3277,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585825</v>
+        <v>585879</v>
       </c>
       <c r="R24" t="n">
-        <v>7084654</v>
+        <v>7084451</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3288,7 +3312,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3298,12 +3322,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,10 +3349,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121347495</v>
+        <v>121346437</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3346,21 +3365,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3370,10 +3389,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>586092</v>
+        <v>585813</v>
       </c>
       <c r="R25" t="n">
-        <v>7084449</v>
+        <v>7084694</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3405,7 +3424,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3415,7 +3434,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,10 +3461,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347511</v>
+        <v>121346810</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3454,25 +3473,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3482,10 +3501,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>586046</v>
+        <v>585874</v>
       </c>
       <c r="R26" t="n">
-        <v>7084490</v>
+        <v>7084559</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3517,7 +3536,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3527,7 +3546,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3542,22 +3561,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347537</v>
+        <v>121347517</v>
       </c>
       <c r="B27" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3570,39 +3589,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585943</v>
+        <v>585965</v>
       </c>
       <c r="R27" t="n">
-        <v>7084462</v>
+        <v>7084448</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3648,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,7 +3658,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3671,10 +3685,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347308</v>
+        <v>121346709</v>
       </c>
       <c r="B28" t="n">
-        <v>98105</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3683,52 +3697,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585988</v>
+        <v>585866</v>
       </c>
       <c r="R28" t="n">
-        <v>7084426</v>
+        <v>7084575</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,19 +3785,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121347539</v>
+        <v>121346558</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585948</v>
+        <v>585813</v>
       </c>
       <c r="R29" t="n">
-        <v>7084466</v>
+        <v>7084662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121346576</v>
+        <v>121347539</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585803</v>
+        <v>585948</v>
       </c>
       <c r="R2" t="n">
-        <v>7084658</v>
+        <v>7084466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346622</v>
+        <v>121347537</v>
       </c>
       <c r="B3" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585815</v>
+        <v>585943</v>
       </c>
       <c r="R3" t="n">
-        <v>7084624</v>
+        <v>7084462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,22 +892,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347308</v>
+        <v>121346810</v>
       </c>
       <c r="B4" t="n">
-        <v>98105</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,52 +916,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585988</v>
+        <v>585874</v>
       </c>
       <c r="R4" t="n">
-        <v>7084426</v>
+        <v>7084559</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347537</v>
+        <v>121347424</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,16 +1032,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1070,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585943</v>
+        <v>586076</v>
       </c>
       <c r="R5" t="n">
-        <v>7084462</v>
+        <v>7084414</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346703</v>
+        <v>121346522</v>
       </c>
       <c r="B6" t="n">
-        <v>98105</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,40 +1150,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1196,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585863</v>
+        <v>585825</v>
       </c>
       <c r="R6" t="n">
-        <v>7084578</v>
+        <v>7084654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1241,7 +1228,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1260,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347731</v>
+        <v>121346709</v>
       </c>
       <c r="B7" t="n">
         <v>78609</v>
@@ -1308,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585899</v>
+        <v>585866</v>
       </c>
       <c r="R7" t="n">
-        <v>7084492</v>
+        <v>7084575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1343,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1353,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346096</v>
+        <v>121347327</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1420,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585791</v>
+        <v>586037</v>
       </c>
       <c r="R8" t="n">
-        <v>7084728</v>
+        <v>7084389</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1465,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1604,10 +1596,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346000</v>
+        <v>121347310</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1620,21 +1612,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1644,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585818</v>
+        <v>585983</v>
       </c>
       <c r="R10" t="n">
-        <v>7084786</v>
+        <v>7084425</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,12 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,7 +1708,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121346034</v>
+        <v>121347495</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1761,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585813</v>
+        <v>586092</v>
       </c>
       <c r="R11" t="n">
-        <v>7084756</v>
+        <v>7084449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1806,7 +1793,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,22 +1808,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347298</v>
+        <v>121347731</v>
       </c>
       <c r="B12" t="n">
-        <v>57509</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1849,51 +1836,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585969</v>
+        <v>585899</v>
       </c>
       <c r="R12" t="n">
-        <v>7084411</v>
+        <v>7084492</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1922,7 +1895,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1932,7 +1905,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,22 +1920,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347511</v>
+        <v>121346594</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>98105</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,38 +1944,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>586046</v>
+        <v>585801</v>
       </c>
       <c r="R13" t="n">
-        <v>7084490</v>
+        <v>7084642</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2034,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2044,7 +2021,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347424</v>
+        <v>121347308</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,43 +2060,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586076</v>
+        <v>585988</v>
       </c>
       <c r="R14" t="n">
-        <v>7084414</v>
+        <v>7084426</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2151,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2161,12 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,7 +2174,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346594</v>
+        <v>121346703</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2228,7 +2209,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2237,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585801</v>
+        <v>585863</v>
       </c>
       <c r="R15" t="n">
-        <v>7084642</v>
+        <v>7084578</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2272,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2282,7 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2297,22 +2288,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346522</v>
+        <v>121346543</v>
       </c>
       <c r="B16" t="n">
-        <v>57356</v>
+        <v>98105</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2321,31 +2312,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2354,10 +2344,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585825</v>
+        <v>585822</v>
       </c>
       <c r="R16" t="n">
-        <v>7084654</v>
+        <v>7084651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2389,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,12 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,22 +2404,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346543</v>
+        <v>121346576</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,42 +2428,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585822</v>
+        <v>585803</v>
       </c>
       <c r="R17" t="n">
-        <v>7084651</v>
+        <v>7084658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2510,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2520,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2547,10 +2528,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347019</v>
+        <v>121346437</v>
       </c>
       <c r="B18" t="n">
-        <v>98105</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2559,42 +2540,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585857</v>
+        <v>585813</v>
       </c>
       <c r="R18" t="n">
-        <v>7084489</v>
+        <v>7084694</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2626,7 +2603,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2636,7 +2613,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347539</v>
+        <v>121347298</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>57509</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,37 +2656,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585948</v>
+        <v>585969</v>
       </c>
       <c r="R19" t="n">
-        <v>7084466</v>
+        <v>7084411</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2738,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,7 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,19 +2754,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347327</v>
+        <v>121346096</v>
       </c>
       <c r="B20" t="n">
         <v>78609</v>
@@ -2815,10 +2806,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>586037</v>
+        <v>585791</v>
       </c>
       <c r="R20" t="n">
-        <v>7084389</v>
+        <v>7084728</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2850,7 +2841,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2860,7 +2851,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2887,7 +2878,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347310</v>
+        <v>121347511</v>
       </c>
       <c r="B21" t="n">
         <v>78609</v>
@@ -2927,10 +2918,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585983</v>
+        <v>586046</v>
       </c>
       <c r="R21" t="n">
-        <v>7084425</v>
+        <v>7084490</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2962,7 +2953,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2972,7 +2963,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2999,7 +2990,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121347495</v>
+        <v>121346558</v>
       </c>
       <c r="B22" t="n">
         <v>78609</v>
@@ -3039,10 +3030,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>586092</v>
+        <v>585813</v>
       </c>
       <c r="R22" t="n">
-        <v>7084449</v>
+        <v>7084662</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3065,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3075,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3111,7 +3102,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346435</v>
+        <v>121347517</v>
       </c>
       <c r="B23" t="n">
         <v>78609</v>
@@ -3151,10 +3142,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585819</v>
+        <v>585965</v>
       </c>
       <c r="R23" t="n">
-        <v>7084684</v>
+        <v>7084448</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3186,7 +3177,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3196,7 +3187,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3223,7 +3214,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347155</v>
+        <v>121347019</v>
       </c>
       <c r="B24" t="n">
         <v>98105</v>
@@ -3258,17 +3249,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3277,10 +3258,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585879</v>
+        <v>585857</v>
       </c>
       <c r="R24" t="n">
-        <v>7084451</v>
+        <v>7084489</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3312,7 +3293,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3322,7 +3303,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3337,22 +3318,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346437</v>
+        <v>121346622</v>
       </c>
       <c r="B25" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3365,21 +3346,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3389,10 +3370,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585813</v>
+        <v>585815</v>
       </c>
       <c r="R25" t="n">
-        <v>7084694</v>
+        <v>7084624</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3424,7 +3405,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3434,7 +3415,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,10 +3442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121346810</v>
+        <v>121347155</v>
       </c>
       <c r="B26" t="n">
-        <v>97059</v>
+        <v>98105</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3473,38 +3454,52 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585874</v>
+        <v>585879</v>
       </c>
       <c r="R26" t="n">
-        <v>7084559</v>
+        <v>7084451</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3536,7 +3531,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3546,7 +3541,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3573,10 +3568,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121347517</v>
+        <v>121346000</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3589,21 +3584,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3613,10 +3608,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585965</v>
+        <v>585818</v>
       </c>
       <c r="R27" t="n">
-        <v>7084448</v>
+        <v>7084786</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3648,7 +3643,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3658,7 +3653,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3673,19 +3673,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346709</v>
+        <v>121346034</v>
       </c>
       <c r="B28" t="n">
         <v>78609</v>
@@ -3725,10 +3725,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585866</v>
+        <v>585813</v>
       </c>
       <c r="R28" t="n">
-        <v>7084575</v>
+        <v>7084756</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,19 +3785,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346558</v>
+        <v>121346435</v>
       </c>
       <c r="B29" t="n">
         <v>78609</v>
@@ -3837,10 +3837,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585813</v>
+        <v>585819</v>
       </c>
       <c r="R29" t="n">
-        <v>7084662</v>
+        <v>7084684</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3897,12 +3897,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -1372,7 +1372,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347327</v>
+        <v>121347310</v>
       </c>
       <c r="B8" t="n">
         <v>78609</v>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586037</v>
+        <v>585983</v>
       </c>
       <c r="R8" t="n">
-        <v>7084389</v>
+        <v>7084425</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,7 +1484,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121346090</v>
+        <v>121347327</v>
       </c>
       <c r="B9" t="n">
         <v>78609</v>
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585825</v>
+        <v>586037</v>
       </c>
       <c r="R9" t="n">
-        <v>7084709</v>
+        <v>7084389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,19 +1584,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121347310</v>
+        <v>121346090</v>
       </c>
       <c r="B10" t="n">
         <v>78609</v>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585983</v>
+        <v>585825</v>
       </c>
       <c r="R10" t="n">
-        <v>7084425</v>
+        <v>7084709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,12 +1696,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347308</v>
+        <v>121346576</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,52 +2060,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585988</v>
+        <v>585803</v>
       </c>
       <c r="R14" t="n">
-        <v>7084426</v>
+        <v>7084658</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2123,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2133,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,19 +2148,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346703</v>
+        <v>121347308</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2209,7 +2195,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2228,10 +2214,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585863</v>
+        <v>585988</v>
       </c>
       <c r="R15" t="n">
-        <v>7084578</v>
+        <v>7084426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2249,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2259,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,7 +2286,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346543</v>
+        <v>121346703</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2335,7 +2321,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2344,10 +2340,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585822</v>
+        <v>585863</v>
       </c>
       <c r="R16" t="n">
-        <v>7084651</v>
+        <v>7084578</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2385,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,22 +2400,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346576</v>
+        <v>121346543</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,38 +2424,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585803</v>
+        <v>585822</v>
       </c>
       <c r="R17" t="n">
-        <v>7084658</v>
+        <v>7084651</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -2048,10 +2048,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121346576</v>
+        <v>121347308</v>
       </c>
       <c r="B14" t="n">
-        <v>90720</v>
+        <v>98105</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,38 +2060,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585803</v>
+        <v>585988</v>
       </c>
       <c r="R14" t="n">
-        <v>7084658</v>
+        <v>7084426</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2123,7 +2137,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2133,7 +2147,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,19 +2162,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121347308</v>
+        <v>121346703</v>
       </c>
       <c r="B15" t="n">
         <v>98105</v>
@@ -2195,7 +2209,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2214,10 +2228,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585988</v>
+        <v>585863</v>
       </c>
       <c r="R15" t="n">
-        <v>7084426</v>
+        <v>7084578</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2249,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2259,7 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2286,7 +2300,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346703</v>
+        <v>121346543</v>
       </c>
       <c r="B16" t="n">
         <v>98105</v>
@@ -2321,17 +2335,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2340,10 +2344,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585863</v>
+        <v>585822</v>
       </c>
       <c r="R16" t="n">
-        <v>7084578</v>
+        <v>7084651</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,7 +2379,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2385,7 +2389,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,22 +2404,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346543</v>
+        <v>121346576</v>
       </c>
       <c r="B17" t="n">
-        <v>98105</v>
+        <v>90720</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2424,42 +2428,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585822</v>
+        <v>585803</v>
       </c>
       <c r="R17" t="n">
-        <v>7084651</v>
+        <v>7084658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121347539</v>
+        <v>121346435</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585948</v>
+        <v>585819</v>
       </c>
       <c r="R2" t="n">
-        <v>7084466</v>
+        <v>7084684</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121347537</v>
+        <v>121347424</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585943</v>
+        <v>586076</v>
       </c>
       <c r="R3" t="n">
-        <v>7084462</v>
+        <v>7084414</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121346810</v>
+        <v>121347019</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>98113</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +921,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>585874</v>
+        <v>585857</v>
       </c>
       <c r="R4" t="n">
-        <v>7084559</v>
+        <v>7084489</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121347424</v>
+        <v>121347731</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,39 +1041,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>586076</v>
+        <v>585899</v>
       </c>
       <c r="R5" t="n">
-        <v>7084414</v>
+        <v>7084492</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1125,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346522</v>
+        <v>121346543</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,31 +1149,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1183,10 +1181,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585825</v>
+        <v>585822</v>
       </c>
       <c r="R6" t="n">
-        <v>7084654</v>
+        <v>7084651</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,12 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1248,22 +1241,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346709</v>
+        <v>121346522</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1276,34 +1269,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585866</v>
+        <v>585825</v>
       </c>
       <c r="R7" t="n">
-        <v>7084575</v>
+        <v>7084654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1335,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1345,7 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347310</v>
+        <v>121347511</v>
       </c>
       <c r="B8" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,10 +1415,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585983</v>
+        <v>586046</v>
       </c>
       <c r="R8" t="n">
-        <v>7084425</v>
+        <v>7084490</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347327</v>
+        <v>121347539</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,10 +1527,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>586037</v>
+        <v>585948</v>
       </c>
       <c r="R9" t="n">
-        <v>7084389</v>
+        <v>7084466</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1572,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1596,10 +1599,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346090</v>
+        <v>121346558</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,10 +1639,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585825</v>
+        <v>585813</v>
       </c>
       <c r="R10" t="n">
-        <v>7084709</v>
+        <v>7084662</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1674,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1684,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1699,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347495</v>
+        <v>121346034</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,10 +1751,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>586092</v>
+        <v>585813</v>
       </c>
       <c r="R11" t="n">
-        <v>7084449</v>
+        <v>7084756</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1783,7 +1786,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1796,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,22 +1811,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121347731</v>
+        <v>121346000</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1836,21 +1839,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1860,10 +1863,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585899</v>
+        <v>585818</v>
       </c>
       <c r="R12" t="n">
-        <v>7084492</v>
+        <v>7084786</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1898,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1908,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1940,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121346594</v>
+        <v>121346090</v>
       </c>
       <c r="B13" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1944,42 +1952,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585801</v>
+        <v>585825</v>
       </c>
       <c r="R13" t="n">
-        <v>7084642</v>
+        <v>7084709</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2011,7 +2015,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,7 +2025,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2036,22 +2040,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347308</v>
+        <v>121347327</v>
       </c>
       <c r="B14" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2060,52 +2064,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>585988</v>
+        <v>586037</v>
       </c>
       <c r="R14" t="n">
-        <v>7084426</v>
+        <v>7084389</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2137,7 +2127,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2147,7 +2137,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2162,22 +2152,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346703</v>
+        <v>121347495</v>
       </c>
       <c r="B15" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2186,52 +2176,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585863</v>
+        <v>586092</v>
       </c>
       <c r="R15" t="n">
-        <v>7084578</v>
+        <v>7084449</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2239,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,22 +2264,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346543</v>
+        <v>121346576</v>
       </c>
       <c r="B16" t="n">
-        <v>98105</v>
+        <v>90728</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,42 +2288,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585822</v>
+        <v>585803</v>
       </c>
       <c r="R16" t="n">
-        <v>7084651</v>
+        <v>7084658</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2379,7 +2351,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2389,7 +2361,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,10 +2388,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121346576</v>
+        <v>121347308</v>
       </c>
       <c r="B17" t="n">
-        <v>90720</v>
+        <v>98113</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,38 +2400,52 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585803</v>
+        <v>585988</v>
       </c>
       <c r="R17" t="n">
-        <v>7084658</v>
+        <v>7084426</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,22 +2502,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121346437</v>
+        <v>121347517</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,21 +2530,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2568,10 +2554,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585813</v>
+        <v>585965</v>
       </c>
       <c r="R18" t="n">
-        <v>7084694</v>
+        <v>7084448</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2603,7 +2589,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2613,7 +2599,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2628,22 +2614,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121347298</v>
+        <v>121346594</v>
       </c>
       <c r="B19" t="n">
-        <v>57509</v>
+        <v>98113</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2652,55 +2638,45 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585969</v>
+        <v>585801</v>
       </c>
       <c r="R19" t="n">
-        <v>7084411</v>
+        <v>7084642</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2729,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,22 +2730,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121346096</v>
+        <v>121346703</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2778,38 +2754,52 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585791</v>
+        <v>585863</v>
       </c>
       <c r="R20" t="n">
-        <v>7084728</v>
+        <v>7084578</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2841,7 +2831,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2851,7 +2841,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2866,22 +2856,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121347511</v>
+        <v>121347537</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,34 +2884,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>586046</v>
+        <v>585943</v>
       </c>
       <c r="R21" t="n">
-        <v>7084490</v>
+        <v>7084462</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2953,7 +2948,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2963,7 +2958,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2978,22 +2973,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346558</v>
+        <v>121347298</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>57510</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3006,37 +3001,51 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585813</v>
+        <v>585969</v>
       </c>
       <c r="R22" t="n">
-        <v>7084662</v>
+        <v>7084411</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3065,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3075,7 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3090,22 +3099,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121347517</v>
+        <v>121346096</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3142,10 +3151,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585965</v>
+        <v>585791</v>
       </c>
       <c r="R23" t="n">
-        <v>7084448</v>
+        <v>7084728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3177,7 +3186,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3187,7 +3196,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3202,22 +3211,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347019</v>
+        <v>121346622</v>
       </c>
       <c r="B24" t="n">
-        <v>98105</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,42 +3235,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585857</v>
+        <v>585815</v>
       </c>
       <c r="R24" t="n">
-        <v>7084489</v>
+        <v>7084624</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3293,7 +3298,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3303,7 +3308,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3330,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346622</v>
+        <v>121347310</v>
       </c>
       <c r="B25" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3370,10 +3375,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585815</v>
+        <v>585983</v>
       </c>
       <c r="R25" t="n">
-        <v>7084624</v>
+        <v>7084425</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3405,7 +3410,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3415,7 +3420,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3442,10 +3447,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347155</v>
+        <v>121346810</v>
       </c>
       <c r="B26" t="n">
-        <v>98105</v>
+        <v>97067</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3454,52 +3459,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585879</v>
+        <v>585874</v>
       </c>
       <c r="R26" t="n">
-        <v>7084451</v>
+        <v>7084559</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3531,7 +3522,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3541,7 +3532,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3568,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346000</v>
+        <v>121346437</v>
       </c>
       <c r="B27" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3584,21 +3575,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3608,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585818</v>
+        <v>585813</v>
       </c>
       <c r="R27" t="n">
-        <v>7084786</v>
+        <v>7084694</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3643,7 +3634,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3653,12 +3644,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3685,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346034</v>
+        <v>121346709</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3725,10 +3711,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585813</v>
+        <v>585866</v>
       </c>
       <c r="R28" t="n">
-        <v>7084756</v>
+        <v>7084575</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3760,7 +3746,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3770,7 +3756,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3785,22 +3771,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346435</v>
+        <v>121347155</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>98113</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3809,38 +3795,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585819</v>
+        <v>585879</v>
       </c>
       <c r="R29" t="n">
-        <v>7084684</v>
+        <v>7084451</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3872,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121346522</v>
+        <v>121347511</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,39 +1269,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>585825</v>
+        <v>586046</v>
       </c>
       <c r="R7" t="n">
-        <v>7084654</v>
+        <v>7084490</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1343,12 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,22 +1353,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121347511</v>
+        <v>121346522</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1391,34 +1381,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>586046</v>
+        <v>585825</v>
       </c>
       <c r="R8" t="n">
-        <v>7084490</v>
+        <v>7084654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,7 +1445,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1460,7 +1455,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,12 +1475,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346437</v>
+        <v>121346709</v>
       </c>
       <c r="B27" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3575,21 +3575,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585813</v>
+        <v>585866</v>
       </c>
       <c r="R27" t="n">
-        <v>7084694</v>
+        <v>7084575</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3634,7 +3634,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3671,10 +3671,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121346709</v>
+        <v>121346437</v>
       </c>
       <c r="B28" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3687,21 +3687,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3711,10 +3711,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>585866</v>
+        <v>585813</v>
       </c>
       <c r="R28" t="n">
-        <v>7084575</v>
+        <v>7084694</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347511</v>
+        <v>121346522</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,34 +1269,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586046</v>
+        <v>585825</v>
       </c>
       <c r="R7" t="n">
-        <v>7084490</v>
+        <v>7084654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1333,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1343,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,22 +1363,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346522</v>
+        <v>121347511</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,39 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585825</v>
+        <v>586046</v>
       </c>
       <c r="R8" t="n">
-        <v>7084654</v>
+        <v>7084490</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1445,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1455,12 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,12 +1475,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121346576</v>
+        <v>121347308</v>
       </c>
       <c r="B16" t="n">
-        <v>90728</v>
+        <v>98113</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2288,38 +2288,52 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585803</v>
+        <v>585988</v>
       </c>
       <c r="R16" t="n">
-        <v>7084658</v>
+        <v>7084426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2351,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2361,7 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2376,22 +2390,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347308</v>
+        <v>121346576</v>
       </c>
       <c r="B17" t="n">
-        <v>98113</v>
+        <v>90728</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2400,52 +2414,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585988</v>
+        <v>585803</v>
       </c>
       <c r="R17" t="n">
-        <v>7084426</v>
+        <v>7084658</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,22 +2502,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347517</v>
+        <v>121346594</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>98113</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,38 +2526,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585965</v>
+        <v>585801</v>
       </c>
       <c r="R18" t="n">
-        <v>7084448</v>
+        <v>7084642</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2589,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2599,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,22 +2618,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346594</v>
+        <v>121347517</v>
       </c>
       <c r="B19" t="n">
-        <v>98113</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2638,42 +2642,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585801</v>
+        <v>585965</v>
       </c>
       <c r="R19" t="n">
-        <v>7084642</v>
+        <v>7084448</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,12 +2730,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121346522</v>
+        <v>121346576</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>585825</v>
+        <v>585803</v>
       </c>
       <c r="R2" t="n">
-        <v>7084654</v>
+        <v>7084658</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121346543</v>
+        <v>121346034</v>
       </c>
       <c r="B3" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,38 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>585822</v>
+        <v>585813</v>
       </c>
       <c r="R3" t="n">
-        <v>7084651</v>
+        <v>7084756</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,31 +877,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121347511</v>
+        <v>121346090</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -953,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>586046</v>
+        <v>585825</v>
       </c>
       <c r="R4" t="n">
-        <v>7084490</v>
+        <v>7084709</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,49 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121346810</v>
+        <v>121346096</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1065,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>585874</v>
+        <v>585791</v>
       </c>
       <c r="R5" t="n">
-        <v>7084559</v>
+        <v>7084728</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1100,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1110,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,31 +1091,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121346709</v>
+        <v>121346435</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1177,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>585866</v>
+        <v>585819</v>
       </c>
       <c r="R6" t="n">
-        <v>7084575</v>
+        <v>7084684</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1212,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,31 +1198,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121347327</v>
+        <v>121346558</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1289,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>586037</v>
+        <v>585813</v>
       </c>
       <c r="R7" t="n">
-        <v>7084389</v>
+        <v>7084662</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1324,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121346594</v>
+        <v>121346622</v>
       </c>
       <c r="B8" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,38 +1328,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>585801</v>
+        <v>585815</v>
       </c>
       <c r="R8" t="n">
-        <v>7084642</v>
+        <v>7084624</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1450,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,19 +1424,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121347539</v>
+        <v>121346709</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1517,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>585948</v>
+        <v>585866</v>
       </c>
       <c r="R9" t="n">
-        <v>7084466</v>
+        <v>7084575</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1552,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1562,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,37 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121346000</v>
+        <v>121347269</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1629,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>585818</v>
+        <v>585963</v>
       </c>
       <c r="R10" t="n">
-        <v>7084786</v>
+        <v>7084395</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1664,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1674,12 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:07</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,67 +1638,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121347298</v>
+        <v>121347310</v>
       </c>
       <c r="B11" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>585969</v>
+        <v>585983</v>
       </c>
       <c r="R11" t="n">
-        <v>7084411</v>
+        <v>7084425</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1795,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1805,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,31 +1733,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121346090</v>
+        <v>121347327</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1872,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>585825</v>
+        <v>586037</v>
       </c>
       <c r="R12" t="n">
-        <v>7084709</v>
+        <v>7084389</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1917,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,67 +1840,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121347537</v>
+        <v>121347495</v>
       </c>
       <c r="B13" t="n">
-        <v>57373</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>585943</v>
+        <v>586092</v>
       </c>
       <c r="R13" t="n">
-        <v>7084462</v>
+        <v>7084449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2024,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2034,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,31 +1947,26 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121347495</v>
+        <v>121347511</v>
       </c>
       <c r="B14" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2101,10 +1994,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>586092</v>
+        <v>586046</v>
       </c>
       <c r="R14" t="n">
-        <v>7084449</v>
+        <v>7084490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2136,7 +2029,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2146,7 +2039,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,19 +2066,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121346558</v>
+        <v>121347517</v>
       </c>
       <c r="B15" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2213,10 +2101,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>585813</v>
+        <v>585965</v>
       </c>
       <c r="R15" t="n">
-        <v>7084662</v>
+        <v>7084448</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2136,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,7 +2146,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,31 +2161,26 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121347517</v>
+        <v>121347539</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2325,10 +2208,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>585965</v>
+        <v>585948</v>
       </c>
       <c r="R16" t="n">
-        <v>7084448</v>
+        <v>7084466</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2243,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2253,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2385,31 +2268,26 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121347310</v>
+        <v>121347731</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2437,10 +2315,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>585983</v>
+        <v>585899</v>
       </c>
       <c r="R17" t="n">
-        <v>7084425</v>
+        <v>7084492</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2472,7 +2350,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2482,7 +2360,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,54 +2387,50 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121347019</v>
+        <v>121347537</v>
       </c>
       <c r="B18" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>6</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>585857</v>
+        <v>585943</v>
       </c>
       <c r="R18" t="n">
-        <v>7084489</v>
+        <v>7084462</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,27 +2487,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121346096</v>
+        <v>121346000</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2641,21 +2510,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2665,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>585791</v>
+        <v>585818</v>
       </c>
       <c r="R19" t="n">
-        <v>7084728</v>
+        <v>7084786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,7 +2579,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2737,52 +2611,38 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121347308</v>
+        <v>121346522</v>
       </c>
       <c r="B20" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2791,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>585988</v>
+        <v>585825</v>
       </c>
       <c r="R20" t="n">
-        <v>7084426</v>
+        <v>7084654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2836,7 +2696,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,15 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121346622</v>
+        <v>121347256</v>
       </c>
       <c r="B21" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2879,34 +2739,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>585815</v>
+        <v>585962</v>
       </c>
       <c r="R21" t="n">
-        <v>7084624</v>
+        <v>7084394</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2938,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2948,7 +2808,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,76 +2828,62 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121346703</v>
+        <v>121347424</v>
       </c>
       <c r="B22" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>585863</v>
+        <v>586076</v>
       </c>
       <c r="R22" t="n">
-        <v>7084578</v>
+        <v>7084414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3064,7 +2915,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3074,7 +2925,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3101,15 +2957,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121346435</v>
+        <v>121347298</v>
       </c>
       <c r="B23" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3117,37 +2968,51 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>585819</v>
+        <v>585969</v>
       </c>
       <c r="R23" t="n">
-        <v>7084684</v>
+        <v>7084411</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3176,7 +3041,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3186,7 +3051,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3213,50 +3078,49 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121347731</v>
+        <v>121346543</v>
       </c>
       <c r="B24" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>585899</v>
+        <v>585822</v>
       </c>
       <c r="R24" t="n">
-        <v>7084492</v>
+        <v>7084651</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3288,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3298,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3325,50 +3189,49 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121346576</v>
+        <v>121346594</v>
       </c>
       <c r="B25" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>585803</v>
+        <v>585801</v>
       </c>
       <c r="R25" t="n">
-        <v>7084658</v>
+        <v>7084642</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3400,7 +3263,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3410,7 +3273,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3437,15 +3300,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121347155</v>
+        <v>121346703</v>
       </c>
       <c r="B26" t="n">
-        <v>98113</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3472,7 +3330,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3491,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>585879</v>
+        <v>585863</v>
       </c>
       <c r="R26" t="n">
-        <v>7084451</v>
+        <v>7084578</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3526,7 +3384,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3536,7 +3394,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3563,50 +3421,49 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121346437</v>
+        <v>121347019</v>
       </c>
       <c r="B27" t="n">
-        <v>90746</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>585813</v>
+        <v>585857</v>
       </c>
       <c r="R27" t="n">
-        <v>7084694</v>
+        <v>7084489</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3638,7 +3495,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3648,7 +3505,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3675,55 +3532,59 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121347424</v>
+        <v>121347155</v>
       </c>
       <c r="B28" t="n">
-        <v>57357</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kärmsjöhöjdens vindkraftspark, Kärmsjöhöjdens vindkraftspark, Ång</t>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>586076</v>
+        <v>585879</v>
       </c>
       <c r="R28" t="n">
-        <v>7084414</v>
+        <v>7084451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3755,7 +3616,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3765,12 +3626,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3797,50 +3653,59 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121346034</v>
+        <v>121347308</v>
       </c>
       <c r="B29" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>585813</v>
+        <v>585988</v>
       </c>
       <c r="R29" t="n">
-        <v>7084756</v>
+        <v>7084426</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3872,7 +3737,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3882,7 +3747,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3906,6 +3771,113 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121346810</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kärmsjöbäcken, Kärmsjöbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>585874</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7084559</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-11-26</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38294-2024 artfynd.xlsx
+++ b/artfynd/A 38294-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346576</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346034</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346090</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346096</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346435</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346558</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346622</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346709</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347269</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347310</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347327</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347495</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347511</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347517</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347539</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347731</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347537</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2608,6 +2698,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346000</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2725,6 +2820,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346522</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2837,6 +2937,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347256</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2954,6 +3059,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347424</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3075,6 +3185,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347298</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3186,6 +3301,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346543</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3297,6 +3417,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346594</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3418,6 +3543,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346703</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3529,6 +3659,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347019</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3650,6 +3785,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347155</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3771,6 +3911,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121347308</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3878,8 +4023,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121346810</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>